--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC71A2C-0CF6-BC43-8A8F-365880FB89B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD70575D-8A14-EA40-9085-C81D54A2B95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4080" yWindow="1420" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="221">
   <si>
     <t>source</t>
   </si>
@@ -280,9 +280,6 @@
   </si>
   <si>
     <t>sts_dx</t>
-  </si>
-  <si>
-    <t>COG_UPR_DX.REG_STAGE_CODE_TEXT,CNS_ON_STUDY_INITIAL_DIAGNOSIS.SUPPTU_QVAL_TUPTDZSTG</t>
   </si>
   <si>
     <t>COG_UPR_DX.REG_STAGE_CODE_TEXT</t>
@@ -1629,7 +1626,7 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1643,7 +1640,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
         <v>26</v>
@@ -1732,16 +1729,16 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
         <v>217</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1755,7 +1752,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
@@ -1807,10 +1804,10 @@
         <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -1830,7 +1827,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -1908,7 +1905,7 @@
         <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -2091,7 +2088,7 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
@@ -2149,10 +2146,10 @@
         <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -2172,7 +2169,7 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
@@ -2230,7 +2227,7 @@
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -2319,7 +2316,7 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -2365,7 +2362,7 @@
         <v>42</v>
       </c>
       <c r="G33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -2445,7 +2442,7 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
@@ -2500,10 +2497,10 @@
         <v>58</v>
       </c>
       <c r="H39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
@@ -2523,7 +2520,7 @@
         <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -2595,7 +2592,7 @@
         <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s">
         <v>17</v>
@@ -2658,7 +2655,7 @@
         <v>36</v>
       </c>
       <c r="G46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -2750,7 +2747,7 @@
         <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2787,7 +2784,7 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
@@ -2842,10 +2839,10 @@
         <v>52</v>
       </c>
       <c r="H54" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J54" t="s">
         <v>17</v>
@@ -2865,10 +2862,10 @@
         <v>23</v>
       </c>
       <c r="F55" t="s">
+        <v>162</v>
+      </c>
+      <c r="G55" t="s">
         <v>163</v>
-      </c>
-      <c r="G55" t="s">
-        <v>164</v>
       </c>
       <c r="J55" t="s">
         <v>54</v>
@@ -2917,7 +2914,7 @@
         <v>36</v>
       </c>
       <c r="G57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
@@ -2940,7 +2937,7 @@
         <v>31</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
@@ -2960,7 +2957,7 @@
         <v>36</v>
       </c>
       <c r="G59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
@@ -3138,7 +3135,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
@@ -3193,10 +3190,10 @@
         <v>58</v>
       </c>
       <c r="H69" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
@@ -3216,10 +3213,10 @@
         <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
@@ -3288,7 +3285,7 @@
         <v>31</v>
       </c>
       <c r="G73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
@@ -3308,7 +3305,7 @@
         <v>36</v>
       </c>
       <c r="G74" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
@@ -3486,7 +3483,7 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
@@ -3541,10 +3538,10 @@
         <v>79</v>
       </c>
       <c r="H84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
@@ -3564,10 +3561,10 @@
         <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G85" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J85" t="s">
         <v>54</v>
@@ -3616,7 +3613,7 @@
         <v>36</v>
       </c>
       <c r="G87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
@@ -3639,7 +3636,7 @@
         <v>31</v>
       </c>
       <c r="G88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
@@ -3659,7 +3656,7 @@
         <v>36</v>
       </c>
       <c r="G89" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
@@ -3837,7 +3834,7 @@
         <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F97" t="s">
         <v>26</v>
@@ -3892,10 +3889,10 @@
         <v>58</v>
       </c>
       <c r="H99" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J99" t="s">
         <v>17</v>
@@ -3915,7 +3912,7 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G100" t="s">
         <v>24</v>
@@ -3990,7 +3987,7 @@
         <v>26</v>
       </c>
       <c r="I103" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -4059,7 +4056,7 @@
         <v>36</v>
       </c>
       <c r="G106" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -4194,7 +4191,7 @@
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F112" t="s">
         <v>26</v>
@@ -4249,10 +4246,10 @@
         <v>52</v>
       </c>
       <c r="H114" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J114" t="s">
         <v>17</v>
@@ -4272,7 +4269,7 @@
         <v>23</v>
       </c>
       <c r="F115" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -4350,7 +4347,7 @@
         <v>26</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -4465,7 +4462,7 @@
         <v>42</v>
       </c>
       <c r="G123" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
@@ -4545,7 +4542,7 @@
         <v>20</v>
       </c>
       <c r="E127" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F127" t="s">
         <v>26</v>
@@ -4600,10 +4597,10 @@
         <v>79</v>
       </c>
       <c r="H129" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I129" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J129" t="s">
         <v>17</v>
@@ -4623,7 +4620,7 @@
         <v>23</v>
       </c>
       <c r="F130" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G130" t="s">
         <v>24</v>
@@ -4698,7 +4695,7 @@
         <v>26</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -4813,7 +4810,7 @@
         <v>42</v>
       </c>
       <c r="G138" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -4899,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="E142" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F142" t="s">
         <v>26</v>
@@ -4957,10 +4954,10 @@
         <v>79</v>
       </c>
       <c r="H144" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I144" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J144" t="s">
         <v>17</v>
@@ -4980,7 +4977,7 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G145" t="s">
         <v>24</v>
@@ -5055,7 +5052,7 @@
         <v>31</v>
       </c>
       <c r="G148" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J148" t="s">
         <v>17</v>
@@ -5250,13 +5247,13 @@
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D157" t="s">
         <v>20</v>
       </c>
       <c r="E157" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F157" t="s">
         <v>26</v>
@@ -5273,7 +5270,7 @@
         <v>10</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D158" t="s">
         <v>20</v>
@@ -5296,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="B159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D159" t="s">
         <v>20</v>
@@ -5311,10 +5308,10 @@
         <v>22</v>
       </c>
       <c r="H159" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J159" t="s">
         <v>17</v>
@@ -5325,7 +5322,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D160" t="s">
         <v>20</v>
@@ -5334,10 +5331,10 @@
         <v>23</v>
       </c>
       <c r="F160" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.2">
@@ -5345,7 +5342,7 @@
         <v>10</v>
       </c>
       <c r="B161" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D161" t="s">
         <v>20</v>
@@ -5368,7 +5365,7 @@
         <v>10</v>
       </c>
       <c r="B162" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C162" t="b">
         <v>1</v>
@@ -5383,7 +5380,7 @@
         <v>36</v>
       </c>
       <c r="G162" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
@@ -5394,7 +5391,7 @@
         <v>10</v>
       </c>
       <c r="B163" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D163" t="s">
         <v>20</v>
@@ -5406,7 +5403,7 @@
         <v>31</v>
       </c>
       <c r="G163" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.2">
@@ -5414,7 +5411,7 @@
         <v>10</v>
       </c>
       <c r="B164" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D164" t="s">
         <v>20</v>
@@ -5426,7 +5423,7 @@
         <v>36</v>
       </c>
       <c r="G164" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.2">
@@ -5434,7 +5431,7 @@
         <v>10</v>
       </c>
       <c r="B165" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D165" t="s">
         <v>20</v>
@@ -5457,7 +5454,7 @@
         <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D166" t="s">
         <v>20</v>
@@ -5480,7 +5477,7 @@
         <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D167" t="s">
         <v>20</v>
@@ -5503,7 +5500,7 @@
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D168" t="s">
         <v>20</v>
@@ -5526,7 +5523,7 @@
         <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D169" t="s">
         <v>20</v>
@@ -5549,7 +5546,7 @@
         <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D170" t="s">
         <v>20</v>
@@ -5575,7 +5572,7 @@
         <v>10</v>
       </c>
       <c r="B171" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
@@ -5598,13 +5595,13 @@
         <v>10</v>
       </c>
       <c r="B172" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D172" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E172" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F172" t="s">
         <v>26</v>
@@ -5613,7 +5610,7 @@
         <v>26</v>
       </c>
       <c r="I172" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.2">
@@ -5621,10 +5618,10 @@
         <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D173" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>72</v>
@@ -5641,25 +5638,25 @@
         <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D174" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F174" t="s">
         <v>74</v>
       </c>
       <c r="G174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H174" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I174" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.2">
@@ -5667,22 +5664,22 @@
         <v>10</v>
       </c>
       <c r="B175" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C175" t="b">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
       </c>
       <c r="G175" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
@@ -5690,19 +5687,19 @@
         <v>10</v>
       </c>
       <c r="B176" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D176" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F176" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G176" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
@@ -5710,22 +5707,22 @@
         <v>10</v>
       </c>
       <c r="B177" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D177" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E177" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F177" t="s">
         <v>36</v>
       </c>
       <c r="G177" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K177" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
@@ -5733,19 +5730,19 @@
         <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D178" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E178" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F178" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G178" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
@@ -5753,19 +5750,19 @@
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D179" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E179" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F179" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G179" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
@@ -5773,13 +5770,13 @@
         <v>10</v>
       </c>
       <c r="B180" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D180" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E180" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F180" t="s">
         <v>26</v>
@@ -5793,13 +5790,13 @@
         <v>10</v>
       </c>
       <c r="B181" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D181" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E181" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F181" t="s">
         <v>26</v>
@@ -5813,13 +5810,13 @@
         <v>10</v>
       </c>
       <c r="B182" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D182" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E182" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F182" t="s">
         <v>26</v>
@@ -5833,13 +5830,13 @@
         <v>10</v>
       </c>
       <c r="B183" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D183" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E183" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F183" t="s">
         <v>26</v>
@@ -5853,13 +5850,13 @@
         <v>10</v>
       </c>
       <c r="B184" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D184" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E184" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F184" t="s">
         <v>26</v>
@@ -5873,13 +5870,13 @@
         <v>10</v>
       </c>
       <c r="B185" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D185" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E185" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F185" t="s">
         <v>26</v>
@@ -5893,13 +5890,13 @@
         <v>10</v>
       </c>
       <c r="B186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D186" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E186" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F186" t="s">
         <v>26</v>
@@ -5913,13 +5910,13 @@
         <v>10</v>
       </c>
       <c r="B187" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D187" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E187" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F187" t="s">
         <v>26</v>
@@ -5928,7 +5925,7 @@
         <v>26</v>
       </c>
       <c r="I187" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
@@ -5936,10 +5933,10 @@
         <v>10</v>
       </c>
       <c r="B188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>72</v>
@@ -5956,31 +5953,31 @@
         <v>10</v>
       </c>
       <c r="B189" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D189" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F189" t="s">
         <v>74</v>
       </c>
       <c r="G189" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H189" t="s">
+        <v>178</v>
+      </c>
+      <c r="I189" t="s">
         <v>179</v>
       </c>
-      <c r="I189" t="s">
-        <v>180</v>
-      </c>
       <c r="J189" t="s">
         <v>17</v>
       </c>
       <c r="K189" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
@@ -5988,19 +5985,19 @@
         <v>10</v>
       </c>
       <c r="B190" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D190" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F190" t="s">
+        <v>182</v>
+      </c>
+      <c r="G190" t="s">
         <v>183</v>
-      </c>
-      <c r="G190" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.2">
@@ -6008,13 +6005,13 @@
         <v>10</v>
       </c>
       <c r="B191" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D191" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F191" t="s">
         <v>26</v>
@@ -6031,13 +6028,13 @@
         <v>10</v>
       </c>
       <c r="B192" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D192" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F192" t="s">
         <v>26</v>
@@ -6054,13 +6051,13 @@
         <v>10</v>
       </c>
       <c r="B193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F193" t="s">
         <v>26</v>
@@ -6077,13 +6074,13 @@
         <v>10</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D194" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E194" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F194" t="s">
         <v>26</v>
@@ -6092,7 +6089,7 @@
         <v>26</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.2">
@@ -6100,10 +6097,10 @@
         <v>10</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D195" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>72</v>
@@ -6120,13 +6117,13 @@
         <v>10</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D196" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F196" t="s">
         <v>13</v>
@@ -6138,7 +6135,7 @@
         <v>73</v>
       </c>
       <c r="I196" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.2">
@@ -6146,13 +6143,13 @@
         <v>10</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D197" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F197" t="s">
         <v>26</v>
@@ -6161,7 +6158,7 @@
         <v>26</v>
       </c>
       <c r="I197" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.2">
@@ -6169,28 +6166,28 @@
         <v>10</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C198" t="b">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F198" t="s">
         <v>36</v>
       </c>
       <c r="G198" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H198" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I198" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.2">
@@ -6198,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D199" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F199" t="s">
         <v>26</v>
@@ -6221,13 +6218,13 @@
         <v>10</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D200" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F200" t="s">
         <v>26</v>
@@ -6247,19 +6244,19 @@
         <v>10</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D201" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F201" t="s">
         <v>36</v>
       </c>
       <c r="G201" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.2">
@@ -6267,13 +6264,13 @@
         <v>10</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D202" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E202" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F202" t="s">
         <v>26</v>
@@ -6287,13 +6284,13 @@
         <v>10</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D203" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E203" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F203" t="s">
         <v>26</v>
@@ -6307,10 +6304,10 @@
         <v>10</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D204" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>33</v>
@@ -6330,10 +6327,10 @@
         <v>10</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D205" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>33</v>
@@ -6350,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D206" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E206" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F206" t="s">
         <v>26</v>
@@ -6365,7 +6362,7 @@
         <v>26</v>
       </c>
       <c r="I206" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.2">
@@ -6373,13 +6370,13 @@
         <v>10</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D207" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E207" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F207" t="s">
         <v>26</v>
@@ -6393,13 +6390,13 @@
         <v>10</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D208" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E208" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F208" t="s">
         <v>26</v>
@@ -6413,13 +6410,13 @@
         <v>10</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D209" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E209" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F209" t="s">
         <v>26</v>
@@ -6433,13 +6430,13 @@
         <v>10</v>
       </c>
       <c r="B210" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D210" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E210" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F210" t="s">
         <v>26</v>
@@ -6448,7 +6445,7 @@
         <v>26</v>
       </c>
       <c r="I210" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.2">
@@ -6456,10 +6453,10 @@
         <v>10</v>
       </c>
       <c r="B211" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D211" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>72</v>
@@ -6476,13 +6473,13 @@
         <v>10</v>
       </c>
       <c r="B212" t="s">
+        <v>117</v>
+      </c>
+      <c r="D212" t="s">
+        <v>117</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D212" t="s">
-        <v>118</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F212" t="s">
         <v>13</v>
@@ -6494,7 +6491,7 @@
         <v>73</v>
       </c>
       <c r="I212" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.2">
@@ -6502,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="B213" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D213" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F213" t="s">
         <v>26</v>
@@ -6525,22 +6522,22 @@
         <v>10</v>
       </c>
       <c r="B214" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C214" t="b">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.2">
@@ -6548,13 +6545,13 @@
         <v>10</v>
       </c>
       <c r="B215" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D215" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F215" t="s">
         <v>26</v>
@@ -6571,13 +6568,13 @@
         <v>10</v>
       </c>
       <c r="B216" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D216" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F216" t="s">
         <v>26</v>
@@ -6594,13 +6591,13 @@
         <v>10</v>
       </c>
       <c r="B217" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D217" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E217" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F217" t="s">
         <v>26</v>
@@ -6609,7 +6606,7 @@
         <v>26</v>
       </c>
       <c r="I217" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.2">
@@ -6617,10 +6614,10 @@
         <v>10</v>
       </c>
       <c r="B218" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D218" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>72</v>
@@ -6637,13 +6634,13 @@
         <v>10</v>
       </c>
       <c r="B219" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D219" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F219" t="s">
         <v>13</v>
@@ -6655,7 +6652,7 @@
         <v>73</v>
       </c>
       <c r="I219" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.2">
@@ -6663,13 +6660,13 @@
         <v>10</v>
       </c>
       <c r="B220" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D220" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F220" t="s">
         <v>26</v>
@@ -6678,10 +6675,10 @@
         <v>26</v>
       </c>
       <c r="I220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J220" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.2">
@@ -6689,25 +6686,25 @@
         <v>10</v>
       </c>
       <c r="B221" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C221" t="b">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F221" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G221" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J221" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.2">
@@ -6715,19 +6712,19 @@
         <v>10</v>
       </c>
       <c r="B222" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D222" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F222" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G222" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J222">
         <v>-999</v>
@@ -6738,19 +6735,19 @@
         <v>10</v>
       </c>
       <c r="B223" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D223" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F223" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G223" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J223">
         <v>-999</v>
@@ -6761,13 +6758,13 @@
         <v>10</v>
       </c>
       <c r="B224" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D224" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F224" t="s">
         <v>26</v>
@@ -6784,22 +6781,22 @@
         <v>10</v>
       </c>
       <c r="B225" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D225" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G225" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I225" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
@@ -6807,13 +6804,13 @@
         <v>10</v>
       </c>
       <c r="B226" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D226" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E226" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F226" t="s">
         <v>26</v>
@@ -6822,7 +6819,7 @@
         <v>26</v>
       </c>
       <c r="I226" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
@@ -6830,10 +6827,10 @@
         <v>10</v>
       </c>
       <c r="B227" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D227" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>72</v>
@@ -6850,13 +6847,13 @@
         <v>10</v>
       </c>
       <c r="B228" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D228" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F228" t="s">
         <v>13</v>
@@ -6868,7 +6865,7 @@
         <v>73</v>
       </c>
       <c r="I228" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
@@ -6876,13 +6873,13 @@
         <v>10</v>
       </c>
       <c r="B229" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D229" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F229" t="s">
         <v>26</v>
@@ -6891,7 +6888,7 @@
         <v>26</v>
       </c>
       <c r="I229" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
@@ -6899,22 +6896,22 @@
         <v>10</v>
       </c>
       <c r="B230" t="s">
+        <v>194</v>
+      </c>
+      <c r="D230" t="s">
+        <v>105</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F230" t="s">
+        <v>26</v>
+      </c>
+      <c r="H230" t="s">
+        <v>26</v>
+      </c>
+      <c r="I230" t="s">
         <v>195</v>
-      </c>
-      <c r="D230" t="s">
-        <v>106</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F230" t="s">
-        <v>26</v>
-      </c>
-      <c r="H230" t="s">
-        <v>26</v>
-      </c>
-      <c r="I230" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
@@ -6922,13 +6919,13 @@
         <v>10</v>
       </c>
       <c r="B231" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D231" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F231" t="s">
         <v>26</v>
@@ -6945,13 +6942,13 @@
         <v>10</v>
       </c>
       <c r="B232" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D232" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F232" t="s">
         <v>26</v>
@@ -6968,22 +6965,22 @@
         <v>10</v>
       </c>
       <c r="B233" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C233" t="b">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F233" t="s">
         <v>36</v>
       </c>
       <c r="G233" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
@@ -6991,13 +6988,13 @@
         <v>10</v>
       </c>
       <c r="B234" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D234" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E234" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F234" t="s">
         <v>26</v>
@@ -7011,13 +7008,13 @@
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D235" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E235" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F235" t="s">
         <v>26</v>
@@ -7031,13 +7028,13 @@
         <v>10</v>
       </c>
       <c r="B236" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D236" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E236" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F236" t="s">
         <v>26</v>
@@ -7051,13 +7048,13 @@
         <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D237" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E237" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F237" t="s">
         <v>26</v>
@@ -7071,13 +7068,13 @@
         <v>10</v>
       </c>
       <c r="B238" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D238" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E238" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F238" t="s">
         <v>26</v>
@@ -7091,13 +7088,13 @@
         <v>10</v>
       </c>
       <c r="B239" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D239" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E239" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F239" t="s">
         <v>26</v>
@@ -7111,13 +7108,13 @@
         <v>10</v>
       </c>
       <c r="B240" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D240" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E240" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F240" t="s">
         <v>26</v>
@@ -7131,13 +7128,13 @@
         <v>10</v>
       </c>
       <c r="B241" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D241" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E241" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F241" t="s">
         <v>26</v>
@@ -7146,7 +7143,7 @@
         <v>26</v>
       </c>
       <c r="I241" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -7154,10 +7151,10 @@
         <v>10</v>
       </c>
       <c r="B242" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D242" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>72</v>
@@ -7174,13 +7171,13 @@
         <v>10</v>
       </c>
       <c r="B243" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D243" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F243" t="s">
         <v>13</v>
@@ -7192,7 +7189,7 @@
         <v>73</v>
       </c>
       <c r="I243" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
@@ -7200,13 +7197,13 @@
         <v>10</v>
       </c>
       <c r="B244" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D244" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F244" t="s">
         <v>26</v>
@@ -7215,7 +7212,7 @@
         <v>26</v>
       </c>
       <c r="I244" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
@@ -7223,13 +7220,13 @@
         <v>10</v>
       </c>
       <c r="B245" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D245" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F245" t="s">
         <v>26</v>
@@ -7238,7 +7235,7 @@
         <v>26</v>
       </c>
       <c r="I245" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -7246,13 +7243,13 @@
         <v>10</v>
       </c>
       <c r="B246" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D246" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F246" t="s">
         <v>26</v>
@@ -7269,13 +7266,13 @@
         <v>10</v>
       </c>
       <c r="B247" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D247" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F247" t="s">
         <v>26</v>
@@ -7292,22 +7289,22 @@
         <v>10</v>
       </c>
       <c r="B248" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C248" t="b">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F248" t="s">
         <v>36</v>
       </c>
       <c r="G248" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
@@ -7315,13 +7312,13 @@
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D249" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E249" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F249" t="s">
         <v>26</v>
@@ -7335,13 +7332,13 @@
         <v>10</v>
       </c>
       <c r="B250" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D250" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E250" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F250" t="s">
         <v>26</v>
@@ -7355,13 +7352,13 @@
         <v>10</v>
       </c>
       <c r="B251" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D251" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E251" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F251" t="s">
         <v>26</v>
@@ -7375,13 +7372,13 @@
         <v>10</v>
       </c>
       <c r="B252" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D252" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E252" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F252" t="s">
         <v>26</v>
@@ -7395,13 +7392,13 @@
         <v>10</v>
       </c>
       <c r="B253" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D253" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E253" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F253" t="s">
         <v>26</v>
@@ -7415,13 +7412,13 @@
         <v>10</v>
       </c>
       <c r="B254" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D254" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E254" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F254" t="s">
         <v>26</v>
@@ -7435,13 +7432,13 @@
         <v>10</v>
       </c>
       <c r="B255" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D255" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E255" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F255" t="s">
         <v>26</v>
@@ -7455,13 +7452,13 @@
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D256" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E256" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F256" t="s">
         <v>26</v>
@@ -7470,7 +7467,7 @@
         <v>26</v>
       </c>
       <c r="I256" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
@@ -7478,10 +7475,10 @@
         <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D257" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>72</v>
@@ -7498,13 +7495,13 @@
         <v>10</v>
       </c>
       <c r="B258" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D258" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F258" t="s">
         <v>13</v>
@@ -7516,7 +7513,7 @@
         <v>73</v>
       </c>
       <c r="I258" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
@@ -7524,13 +7521,13 @@
         <v>10</v>
       </c>
       <c r="B259" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D259" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F259" t="s">
         <v>26</v>
@@ -7539,7 +7536,7 @@
         <v>26</v>
       </c>
       <c r="I259" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
@@ -7547,13 +7544,13 @@
         <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D260" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F260" t="s">
         <v>26</v>
@@ -7562,7 +7559,7 @@
         <v>26</v>
       </c>
       <c r="I260" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
@@ -7570,13 +7567,13 @@
         <v>10</v>
       </c>
       <c r="B261" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D261" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F261" t="s">
         <v>26</v>
@@ -7593,13 +7590,13 @@
         <v>10</v>
       </c>
       <c r="B262" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D262" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F262" t="s">
         <v>26</v>
@@ -7616,22 +7613,22 @@
         <v>10</v>
       </c>
       <c r="B263" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C263" t="b">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F263" t="s">
         <v>36</v>
       </c>
       <c r="G263" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
@@ -7639,13 +7636,13 @@
         <v>10</v>
       </c>
       <c r="B264" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D264" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E264" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F264" t="s">
         <v>26</v>
@@ -7659,13 +7656,13 @@
         <v>10</v>
       </c>
       <c r="B265" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D265" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E265" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F265" t="s">
         <v>26</v>
@@ -7679,13 +7676,13 @@
         <v>10</v>
       </c>
       <c r="B266" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D266" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E266" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F266" t="s">
         <v>26</v>
@@ -7699,13 +7696,13 @@
         <v>10</v>
       </c>
       <c r="B267" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D267" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E267" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F267" t="s">
         <v>26</v>
@@ -7719,13 +7716,13 @@
         <v>10</v>
       </c>
       <c r="B268" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D268" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E268" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F268" t="s">
         <v>26</v>
@@ -7739,13 +7736,13 @@
         <v>10</v>
       </c>
       <c r="B269" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D269" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E269" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F269" t="s">
         <v>26</v>
@@ -7759,13 +7756,13 @@
         <v>10</v>
       </c>
       <c r="B270" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D270" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E270" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F270" t="s">
         <v>26</v>
@@ -7779,13 +7776,13 @@
         <v>10</v>
       </c>
       <c r="B271" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D271" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E271" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F271" t="s">
         <v>26</v>
@@ -7794,7 +7791,7 @@
         <v>26</v>
       </c>
       <c r="I271" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
@@ -7802,10 +7799,10 @@
         <v>10</v>
       </c>
       <c r="B272" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D272" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>72</v>
@@ -7822,13 +7819,13 @@
         <v>10</v>
       </c>
       <c r="B273" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D273" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F273" t="s">
         <v>13</v>
@@ -7840,7 +7837,7 @@
         <v>73</v>
       </c>
       <c r="I273" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
@@ -7848,13 +7845,13 @@
         <v>10</v>
       </c>
       <c r="B274" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D274" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F274" t="s">
         <v>26</v>
@@ -7863,7 +7860,7 @@
         <v>26</v>
       </c>
       <c r="I274" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
@@ -7871,13 +7868,13 @@
         <v>10</v>
       </c>
       <c r="B275" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D275" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F275" t="s">
         <v>26</v>
@@ -7886,7 +7883,7 @@
         <v>26</v>
       </c>
       <c r="I275" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
@@ -7894,13 +7891,13 @@
         <v>10</v>
       </c>
       <c r="B276" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D276" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F276" t="s">
         <v>26</v>
@@ -7917,13 +7914,13 @@
         <v>10</v>
       </c>
       <c r="B277" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D277" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F277" t="s">
         <v>26</v>
@@ -7940,22 +7937,22 @@
         <v>10</v>
       </c>
       <c r="B278" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C278" t="b">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F278" t="s">
         <v>36</v>
       </c>
       <c r="G278" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
@@ -7963,13 +7960,13 @@
         <v>10</v>
       </c>
       <c r="B279" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D279" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E279" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F279" t="s">
         <v>26</v>
@@ -7983,13 +7980,13 @@
         <v>10</v>
       </c>
       <c r="B280" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D280" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E280" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F280" t="s">
         <v>26</v>
@@ -8003,13 +8000,13 @@
         <v>10</v>
       </c>
       <c r="B281" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D281" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E281" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F281" t="s">
         <v>26</v>
@@ -8023,13 +8020,13 @@
         <v>10</v>
       </c>
       <c r="B282" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D282" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E282" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F282" t="s">
         <v>26</v>
@@ -8043,13 +8040,13 @@
         <v>10</v>
       </c>
       <c r="B283" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D283" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E283" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F283" t="s">
         <v>26</v>
@@ -8063,13 +8060,13 @@
         <v>10</v>
       </c>
       <c r="B284" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D284" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E284" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F284" t="s">
         <v>26</v>
@@ -8083,13 +8080,13 @@
         <v>10</v>
       </c>
       <c r="B285" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D285" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E285" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F285" t="s">
         <v>26</v>
@@ -8103,13 +8100,13 @@
         <v>10</v>
       </c>
       <c r="B286" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D286" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E286" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F286" t="s">
         <v>26</v>
@@ -8118,7 +8115,7 @@
         <v>26</v>
       </c>
       <c r="I286" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
@@ -8126,10 +8123,10 @@
         <v>10</v>
       </c>
       <c r="B287" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D287" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>72</v>
@@ -8146,19 +8143,19 @@
         <v>10</v>
       </c>
       <c r="B288" t="s">
+        <v>209</v>
+      </c>
+      <c r="D288" t="s">
+        <v>105</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F288" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G288" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="D288" t="s">
-        <v>106</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G288" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
@@ -8168,13 +8165,13 @@
         <v>10</v>
       </c>
       <c r="B289" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D289" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>26</v>
@@ -8183,7 +8180,7 @@
         <v>26</v>
       </c>
       <c r="I289" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -8191,19 +8188,19 @@
         <v>10</v>
       </c>
       <c r="B290" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D290" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F290" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G290" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -8211,13 +8208,13 @@
         <v>10</v>
       </c>
       <c r="B291" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D291" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F291" t="s">
         <v>26</v>
@@ -8234,13 +8231,13 @@
         <v>10</v>
       </c>
       <c r="B292" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D292" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F292" t="s">
         <v>26</v>
@@ -8257,22 +8254,22 @@
         <v>10</v>
       </c>
       <c r="B293" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C293" t="b">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G293" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
@@ -8280,13 +8277,13 @@
         <v>10</v>
       </c>
       <c r="B294" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D294" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E294" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F294" t="s">
         <v>26</v>
@@ -8300,13 +8297,13 @@
         <v>10</v>
       </c>
       <c r="B295" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D295" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E295" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F295" t="s">
         <v>26</v>
@@ -8320,13 +8317,13 @@
         <v>10</v>
       </c>
       <c r="B296" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D296" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E296" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F296" t="s">
         <v>26</v>
@@ -8340,13 +8337,13 @@
         <v>10</v>
       </c>
       <c r="B297" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D297" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E297" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F297" t="s">
         <v>26</v>
@@ -8360,13 +8357,13 @@
         <v>10</v>
       </c>
       <c r="B298" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D298" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E298" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F298" t="s">
         <v>26</v>
@@ -8380,13 +8377,13 @@
         <v>10</v>
       </c>
       <c r="B299" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D299" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E299" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F299" t="s">
         <v>26</v>
@@ -8400,13 +8397,13 @@
         <v>10</v>
       </c>
       <c r="B300" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D300" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E300" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F300" t="s">
         <v>26</v>
@@ -8435,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -8443,7 +8440,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -8451,7 +8448,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -8459,7 +8456,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8467,7 +8464,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -8475,7 +8472,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -8483,7 +8480,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -8491,7 +8488,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8499,7 +8496,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -8507,7 +8504,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD70575D-8A14-EA40-9085-C81D54A2B95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09510FC5-1A98-714C-8771-D3198F641933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1420" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
+    <workbookView xWindow="2920" yWindow="1620" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="cog_rules" sheetId="1" r:id="rId1"/>
     <sheet name="key" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cog_rules!$A$1:$K$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cog_rules!$A$1:$K$311</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="224">
   <si>
     <t>source</t>
   </si>
@@ -114,9 +114,6 @@
     <t>DEMOGRAPHY.DM_BRTHDAT,COG_UPR_DX.DATE_DIA</t>
   </si>
   <si>
-    <t>diagnosis_classification_system</t>
-  </si>
-  <si>
     <t>default</t>
   </si>
   <si>
@@ -276,9 +273,6 @@
     <t>STS5</t>
   </si>
   <si>
-    <t>DIAGNOSIS_DETAIL_STS.MH_MHSCAT_STSDXINTGRT_NRSTS,DIAGNOSIS_DETAIL_STS.MH_MHSCAT_STSDXINTGRT_RMS,ON_STUDY_DX_SOFT_TISSUE_SARCOMA.STSDXCAT_X1,ON_STUDY_DX_SOFT_TISSUE_SARCOMA.STSDXCAT_X2</t>
-  </si>
-  <si>
     <t>sts_dx</t>
   </si>
   <si>
@@ -700,6 +694,21 @@
   </si>
   <si>
     <t>RADIATION_THERAPY.RT_TX_TP_A1,RADIATION_THERAPY.RT_TX_TP_A2,RADIATION_THERAPY.RT_TX_TP_A3,RADIATION_THERAPY.RT_TX_TP_A4,Tx Chemo:CNS.AGT_ADM_NM_A33,TX_CHEMO_SOFT_TISSUE_SARCOMA.AGT_ADM_NM_A33,TX_CHEMO_RARE_TUMORS.AGT_ADM_NM_A33,TX_CHEMO_OSTEOSARCOMA.AGT_ADM_NM_A33,TX_CHEMO_EWINGS_SARCOMA.AGT_ADM_NM_A33,TX_CHEMO_GERM_CELL_TUMOR.AGT_ADM_NM_A33,TX_CHEMO_LIVER_TUMORS.AGT_ADM_NM_A33</t>
+  </si>
+  <si>
+    <t>submitted_diagnosis_category</t>
+  </si>
+  <si>
+    <t>CNS_DIAGNOSIS_DETAIL.MH_MHCAT_CNSDXCAT,MCI_MOLECULAR_REPORT.MH_MHCAT_CNSDXCAT</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS_DETAIL_STS.STSDXTP,ON_STUDY_DX_SOFT_TISSUE_SARCOMA.STSDXTP,DIAGNOSIS_DETAIL_FORM.GF_GFCAT_DXTYPE</t>
+  </si>
+  <si>
+    <t>ON_STUDY_DX_SOFT_TISSUE_SARCOMA.STSDXCAT_X1,ON_STUDY_DX_SOFT_TISSUE_SARCOMA.STSDXCAT_X2,ON_STUDY_DX_SOFT_TISSUE_SARCOMA.TUMOR_HIST_CAT_SPEC_X1,ON_STUDY_DX_SOFT_TISSUE_SARCOMA.TUMOR_HIST_CAT_SPEC_X2,DIAGNOSIS_DETAIL_FORM.MI_MICAT_RMSTYPE,DIAGNOSIS_DETAIL_FORM.MI_MICAT_NRSTSTYPE,DIAGNOSIS_DETAIL_STS.MH_MHSCAT_STSDXINTGRT_RMS,DIAGNOSIS_DETAIL_STS.MH_MHSCAT_STSDXINTGRT_NRSTS,</t>
+  </si>
+  <si>
+    <t>submitted_diagnosis_classification_system</t>
   </si>
 </sst>
 </file>
@@ -1201,12 +1210,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1582,7 +1592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
-  <dimension ref="A1:K300"/>
+  <dimension ref="A1:K311"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
@@ -1626,7 +1636,7 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1640,13 +1650,13 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -1689,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -1706,7 +1716,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -1729,16 +1739,16 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1752,13 +1762,13 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
         <v>20</v>
@@ -1775,7 +1785,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
@@ -1789,7 +1799,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -1798,16 +1811,16 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -1827,7 +1840,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -1847,16 +1860,16 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
         <v>26</v>
-      </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1870,16 +1883,16 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
         <v>28</v>
-      </c>
-      <c r="F12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1893,19 +1906,19 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
         <v>30</v>
       </c>
-      <c r="F13" t="s">
-        <v>31</v>
-      </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1919,13 +1932,13 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1942,13 +1955,13 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
         <v>35</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>36</v>
-      </c>
-      <c r="G15" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -1962,13 +1975,13 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
         <v>38</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -1982,13 +1995,13 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" t="s">
         <v>40</v>
-      </c>
-      <c r="F17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -2002,13 +2015,13 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" t="s">
         <v>42</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>43</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
@@ -2025,13 +2038,13 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -2045,13 +2058,13 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" t="s">
         <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -2065,16 +2078,16 @@
         <v>20</v>
       </c>
       <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
         <v>48</v>
       </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -2082,19 +2095,19 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -2105,13 +2118,13 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -2128,10 +2141,7 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="b">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
         <v>20</v>
@@ -2140,16 +2150,16 @@
         <v>21</v>
       </c>
       <c r="F24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
         <v>51</v>
       </c>
-      <c r="G24" t="s">
-        <v>52</v>
-      </c>
       <c r="H24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
@@ -2160,7 +2170,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
@@ -2169,13 +2179,13 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -2183,22 +2193,22 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -2206,28 +2216,28 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" t="s">
         <v>28</v>
       </c>
-      <c r="F27" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" t="s">
-        <v>29</v>
-      </c>
       <c r="J27" t="s">
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -2235,19 +2245,19 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
         <v>20</v>
       </c>
       <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
         <v>30</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>31</v>
-      </c>
-      <c r="G28" t="s">
-        <v>32</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -2258,19 +2268,19 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
         <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -2278,19 +2288,19 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>17</v>
@@ -2304,19 +2314,19 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -2324,19 +2334,19 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
         <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>17</v>
@@ -2350,19 +2360,19 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s">
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -2370,13 +2380,13 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" t="s">
         <v>20</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -2387,25 +2397,25 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
         <v>20</v>
       </c>
       <c r="E35" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" t="s">
         <v>46</v>
       </c>
-      <c r="F35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G35" t="s">
-        <v>47</v>
-      </c>
       <c r="H35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -2413,22 +2423,22 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" t="s">
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -2436,19 +2446,19 @@
         <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" t="s">
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I37" t="s">
         <v>20</v>
@@ -2459,13 +2469,13 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38" t="s">
         <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -2479,10 +2489,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" t="b">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
@@ -2491,16 +2498,16 @@
         <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
@@ -2511,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D40" t="s">
         <v>20</v>
@@ -2520,7 +2527,7 @@
         <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -2531,22 +2538,22 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -2554,22 +2561,22 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
       </c>
       <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" t="s">
         <v>28</v>
-      </c>
-      <c r="F42" t="s">
-        <v>26</v>
-      </c>
-      <c r="H42" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" t="s">
-        <v>29</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
@@ -2580,19 +2587,19 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D43" t="s">
         <v>20</v>
       </c>
       <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" t="s">
         <v>30</v>
       </c>
-      <c r="F43" t="s">
-        <v>31</v>
-      </c>
       <c r="G43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s">
         <v>17</v>
@@ -2603,19 +2610,19 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s">
         <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
       </c>
       <c r="G44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -2623,19 +2630,19 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
         <v>20</v>
       </c>
       <c r="E45" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" t="s">
         <v>35</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>36</v>
-      </c>
-      <c r="G45" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -2643,19 +2650,19 @@
         <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D46" t="s">
         <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G46" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -2663,19 +2670,19 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
         <v>20</v>
       </c>
       <c r="E47" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" t="s">
         <v>40</v>
-      </c>
-      <c r="F47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G47" t="s">
-        <v>41</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
@@ -2686,16 +2693,16 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D48" t="s">
         <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
@@ -2706,19 +2713,19 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D49" t="s">
         <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I49" t="s">
         <v>17</v>
@@ -2729,25 +2736,25 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
         <v>20</v>
       </c>
       <c r="E50" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" t="s">
+        <v>73</v>
+      </c>
+      <c r="G50" t="s">
         <v>46</v>
       </c>
-      <c r="F50" t="s">
-        <v>74</v>
-      </c>
-      <c r="G50" t="s">
-        <v>47</v>
-      </c>
       <c r="H50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2755,22 +2762,22 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -2778,19 +2785,19 @@
         <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I52" t="s">
         <v>20</v>
@@ -2801,13 +2808,13 @@
         <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
@@ -2824,7 +2831,7 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D54" t="s">
         <v>20</v>
@@ -2833,16 +2840,16 @@
         <v>21</v>
       </c>
       <c r="F54" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G54" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H54" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J54" t="s">
         <v>17</v>
@@ -2853,7 +2860,7 @@
         <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
         <v>20</v>
@@ -2862,13 +2869,13 @@
         <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G55" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -2876,22 +2883,22 @@
         <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
@@ -2899,7 +2906,7 @@
         <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C57" t="b">
         <v>1</v>
@@ -2908,13 +2915,13 @@
         <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
@@ -2925,19 +2932,19 @@
         <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
       </c>
       <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" t="s">
         <v>30</v>
       </c>
-      <c r="F58" t="s">
-        <v>31</v>
-      </c>
       <c r="G58" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
@@ -2945,19 +2952,19 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G59" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
@@ -2965,19 +2972,19 @@
         <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I60" t="s">
         <v>17</v>
@@ -2988,19 +2995,19 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I61" t="s">
         <v>17</v>
@@ -3011,19 +3018,19 @@
         <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I62" t="s">
         <v>17</v>
@@ -3034,19 +3041,19 @@
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I63" t="s">
         <v>17</v>
@@ -3057,19 +3064,19 @@
         <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
         <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I64" t="s">
         <v>17</v>
@@ -3080,25 +3087,25 @@
         <v>10</v>
       </c>
       <c r="B65" t="s">
+        <v>58</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>45</v>
+      </c>
+      <c r="F65" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" t="s">
+        <v>46</v>
+      </c>
+      <c r="H65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I65" t="s">
         <v>59</v>
-      </c>
-      <c r="D65" t="s">
-        <v>20</v>
-      </c>
-      <c r="E65" t="s">
-        <v>46</v>
-      </c>
-      <c r="F65" t="s">
-        <v>74</v>
-      </c>
-      <c r="G65" t="s">
-        <v>47</v>
-      </c>
-      <c r="H65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I65" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
@@ -3106,22 +3113,22 @@
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I66" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
@@ -3129,19 +3136,19 @@
         <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I67" t="s">
         <v>20</v>
@@ -3152,13 +3159,13 @@
         <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F68" t="s">
         <v>13</v>
@@ -3175,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
@@ -3184,16 +3191,16 @@
         <v>21</v>
       </c>
       <c r="F69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G69" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="H69" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
@@ -3204,7 +3211,7 @@
         <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
@@ -3213,10 +3220,10 @@
         <v>23</v>
       </c>
       <c r="F70" t="s">
+        <v>160</v>
+      </c>
+      <c r="G70" t="s">
         <v>162</v>
-      </c>
-      <c r="G70" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
@@ -3224,22 +3231,22 @@
         <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F71" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H71" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
@@ -3247,7 +3254,7 @@
         <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72" t="b">
         <v>1</v>
@@ -3256,13 +3263,13 @@
         <v>20</v>
       </c>
       <c r="E72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G72" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J72" t="s">
         <v>17</v>
@@ -3273,19 +3280,19 @@
         <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" t="s">
         <v>20</v>
       </c>
       <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" t="s">
         <v>30</v>
       </c>
-      <c r="F73" t="s">
-        <v>31</v>
-      </c>
       <c r="G73" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
@@ -3293,19 +3300,19 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D74" t="s">
         <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G74" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
@@ -3313,19 +3320,19 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D75" t="s">
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I75" t="s">
         <v>17</v>
@@ -3336,19 +3343,19 @@
         <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D76" t="s">
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I76" t="s">
         <v>17</v>
@@ -3359,19 +3366,19 @@
         <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D77" t="s">
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I77" t="s">
         <v>17</v>
@@ -3382,19 +3389,19 @@
         <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D78" t="s">
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I78" t="s">
         <v>17</v>
@@ -3405,19 +3412,19 @@
         <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D79" t="s">
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I79" t="s">
         <v>17</v>
@@ -3428,25 +3435,25 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
       </c>
       <c r="E80" t="s">
+        <v>45</v>
+      </c>
+      <c r="F80" t="s">
+        <v>73</v>
+      </c>
+      <c r="G80" t="s">
         <v>46</v>
       </c>
-      <c r="F80" t="s">
-        <v>74</v>
-      </c>
-      <c r="G80" t="s">
-        <v>47</v>
-      </c>
       <c r="H80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
@@ -3454,22 +3461,22 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D81" t="s">
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
@@ -3477,19 +3484,19 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D82" t="s">
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I82" t="s">
         <v>20</v>
@@ -3500,13 +3507,13 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D83" t="s">
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F83" t="s">
         <v>13</v>
@@ -3522,8 +3529,11 @@
       <c r="A84" t="s">
         <v>10</v>
       </c>
-      <c r="B84" t="s">
-        <v>63</v>
+      <c r="B84" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" t="b">
+        <v>1</v>
       </c>
       <c r="D84" t="s">
         <v>20</v>
@@ -3532,16 +3542,16 @@
         <v>21</v>
       </c>
       <c r="F84" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G84" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="H84" t="s">
-        <v>177</v>
-      </c>
-      <c r="I84" t="s">
-        <v>84</v>
+        <v>174</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
@@ -3552,7 +3562,7 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D85" t="s">
         <v>20</v>
@@ -3561,13 +3571,13 @@
         <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G85" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
@@ -3575,22 +3585,22 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I86" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
@@ -3598,7 +3608,7 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C87" t="b">
         <v>1</v>
@@ -3607,13 +3617,13 @@
         <v>20</v>
       </c>
       <c r="E87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G87" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
@@ -3624,19 +3634,19 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D88" t="s">
         <v>20</v>
       </c>
       <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" t="s">
         <v>30</v>
       </c>
-      <c r="F88" t="s">
-        <v>31</v>
-      </c>
       <c r="G88" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
@@ -3644,19 +3654,19 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D89" t="s">
         <v>20</v>
       </c>
       <c r="E89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G89" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
@@ -3664,19 +3674,19 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D90" t="s">
         <v>20</v>
       </c>
       <c r="E90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I90" t="s">
         <v>17</v>
@@ -3687,19 +3697,19 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D91" t="s">
         <v>20</v>
       </c>
       <c r="E91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I91" t="s">
         <v>17</v>
@@ -3710,19 +3720,19 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D92" t="s">
         <v>20</v>
       </c>
       <c r="E92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I92" t="s">
         <v>17</v>
@@ -3733,19 +3743,19 @@
         <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D93" t="s">
         <v>20</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I93" t="s">
         <v>17</v>
@@ -3756,19 +3766,19 @@
         <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D94" t="s">
         <v>20</v>
       </c>
       <c r="E94" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F94" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H94" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I94" t="s">
         <v>17</v>
@@ -3779,25 +3789,25 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D95" t="s">
         <v>20</v>
       </c>
       <c r="E95" t="s">
+        <v>45</v>
+      </c>
+      <c r="F95" t="s">
+        <v>73</v>
+      </c>
+      <c r="G95" t="s">
         <v>46</v>
       </c>
-      <c r="F95" t="s">
-        <v>74</v>
-      </c>
-      <c r="G95" t="s">
-        <v>47</v>
-      </c>
       <c r="H95" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I95" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
@@ -3805,22 +3815,22 @@
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D96" t="s">
         <v>20</v>
       </c>
       <c r="E96" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
@@ -3828,19 +3838,19 @@
         <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D97" t="s">
         <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F97" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H97" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I97" t="s">
         <v>20</v>
@@ -3851,13 +3861,13 @@
         <v>10</v>
       </c>
       <c r="B98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D98" t="s">
         <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F98" t="s">
         <v>13</v>
@@ -3873,8 +3883,8 @@
       <c r="A99" t="s">
         <v>10</v>
       </c>
-      <c r="B99" t="s">
-        <v>64</v>
+      <c r="B99" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="D99" t="s">
         <v>20</v>
@@ -3883,16 +3893,16 @@
         <v>21</v>
       </c>
       <c r="F99" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G99" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="H99" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J99" t="s">
         <v>17</v>
@@ -3903,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="B100" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D100" t="s">
         <v>20</v>
@@ -3912,7 +3922,7 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G100" t="s">
         <v>24</v>
@@ -3923,22 +3933,22 @@
         <v>10</v>
       </c>
       <c r="B101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D101" t="s">
         <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I101" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
@@ -3946,22 +3956,22 @@
         <v>10</v>
       </c>
       <c r="B102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D102" t="s">
         <v>20</v>
       </c>
       <c r="E102" t="s">
+        <v>27</v>
+      </c>
+      <c r="F102" t="s">
+        <v>25</v>
+      </c>
+      <c r="H102" t="s">
+        <v>25</v>
+      </c>
+      <c r="I102" t="s">
         <v>28</v>
-      </c>
-      <c r="F102" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" t="s">
-        <v>26</v>
-      </c>
-      <c r="I102" t="s">
-        <v>29</v>
       </c>
       <c r="J102" t="s">
         <v>17</v>
@@ -3972,22 +3982,22 @@
         <v>10</v>
       </c>
       <c r="B103" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D103" t="s">
         <v>20</v>
       </c>
       <c r="E103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F103" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H103" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I103" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -3995,7 +4005,7 @@
         <v>10</v>
       </c>
       <c r="B104" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C104" t="b">
         <v>1</v>
@@ -4004,13 +4014,13 @@
         <v>20</v>
       </c>
       <c r="E104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G104" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
@@ -4018,22 +4028,22 @@
         <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D105" t="s">
         <v>20</v>
       </c>
       <c r="E105" t="s">
+        <v>34</v>
+      </c>
+      <c r="F105" t="s">
         <v>35</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>36</v>
       </c>
-      <c r="G105" t="s">
-        <v>37</v>
-      </c>
       <c r="H105" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I105" t="s">
         <v>17</v>
@@ -4044,19 +4054,19 @@
         <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D106" t="s">
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F106" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G106" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -4064,22 +4074,22 @@
         <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D107" t="s">
         <v>20</v>
       </c>
       <c r="E107" t="s">
+        <v>39</v>
+      </c>
+      <c r="F107" t="s">
+        <v>35</v>
+      </c>
+      <c r="G107" t="s">
         <v>40</v>
       </c>
-      <c r="F107" t="s">
-        <v>36</v>
-      </c>
-      <c r="G107" t="s">
-        <v>41</v>
-      </c>
       <c r="H107" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I107" t="s">
         <v>17</v>
@@ -4090,19 +4100,19 @@
         <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D108" t="s">
         <v>20</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I108" t="s">
         <v>17</v>
@@ -4113,19 +4123,19 @@
         <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
       </c>
       <c r="E109" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F109" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H109" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I109" t="s">
         <v>17</v>
@@ -4136,25 +4146,25 @@
         <v>10</v>
       </c>
       <c r="B110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D110" t="s">
         <v>20</v>
       </c>
       <c r="E110" t="s">
+        <v>45</v>
+      </c>
+      <c r="F110" t="s">
+        <v>73</v>
+      </c>
+      <c r="G110" t="s">
         <v>46</v>
       </c>
-      <c r="F110" t="s">
-        <v>74</v>
-      </c>
-      <c r="G110" t="s">
-        <v>47</v>
-      </c>
       <c r="H110" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I110" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
@@ -4162,22 +4172,22 @@
         <v>10</v>
       </c>
       <c r="B111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D111" t="s">
         <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F111" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H111" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I111" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
@@ -4185,19 +4195,19 @@
         <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D112" t="s">
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F112" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H112" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I112" t="s">
         <v>20</v>
@@ -4208,13 +4218,13 @@
         <v>10</v>
       </c>
       <c r="B113" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D113" t="s">
         <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F113" t="s">
         <v>13</v>
@@ -4230,8 +4240,8 @@
       <c r="A114" t="s">
         <v>10</v>
       </c>
-      <c r="B114" t="s">
-        <v>67</v>
+      <c r="B114" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
@@ -4240,16 +4250,16 @@
         <v>21</v>
       </c>
       <c r="F114" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G114" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H114" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J114" t="s">
         <v>17</v>
@@ -4260,7 +4270,7 @@
         <v>10</v>
       </c>
       <c r="B115" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D115" t="s">
         <v>20</v>
@@ -4269,13 +4279,13 @@
         <v>23</v>
       </c>
       <c r="F115" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
       </c>
       <c r="J115" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
@@ -4283,22 +4293,22 @@
         <v>10</v>
       </c>
       <c r="B116" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D116" t="s">
         <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I116" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
@@ -4306,22 +4316,22 @@
         <v>10</v>
       </c>
       <c r="B117" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D117" t="s">
         <v>20</v>
       </c>
       <c r="E117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117" t="s">
+        <v>25</v>
+      </c>
+      <c r="H117" t="s">
+        <v>25</v>
+      </c>
+      <c r="I117" t="s">
         <v>28</v>
-      </c>
-      <c r="F117" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" t="s">
-        <v>26</v>
-      </c>
-      <c r="I117" t="s">
-        <v>29</v>
       </c>
       <c r="J117" t="s">
         <v>17</v>
@@ -4332,22 +4342,22 @@
         <v>10</v>
       </c>
       <c r="B118" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D118" t="s">
         <v>20</v>
       </c>
       <c r="E118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -4355,7 +4365,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C119" t="b">
         <v>1</v>
@@ -4364,13 +4374,13 @@
         <v>20</v>
       </c>
       <c r="E119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F119" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G119" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
@@ -4378,19 +4388,19 @@
         <v>10</v>
       </c>
       <c r="B120" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D120" t="s">
         <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F120" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H120" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I120" t="s">
         <v>17</v>
@@ -4401,19 +4411,19 @@
         <v>10</v>
       </c>
       <c r="B121" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D121" t="s">
         <v>20</v>
       </c>
       <c r="E121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I121" t="s">
         <v>17</v>
@@ -4424,19 +4434,19 @@
         <v>10</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D122" t="s">
         <v>20</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F122" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H122" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I122" t="s">
         <v>17</v>
@@ -4450,19 +4460,19 @@
         <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D123" t="s">
         <v>20</v>
       </c>
       <c r="E123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G123" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
@@ -4470,13 +4480,13 @@
         <v>10</v>
       </c>
       <c r="B124" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D124" t="s">
         <v>20</v>
       </c>
       <c r="E124" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F124" t="s">
         <v>13</v>
@@ -4487,25 +4497,25 @@
         <v>10</v>
       </c>
       <c r="B125" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D125" t="s">
         <v>20</v>
       </c>
       <c r="E125" t="s">
+        <v>45</v>
+      </c>
+      <c r="F125" t="s">
+        <v>73</v>
+      </c>
+      <c r="G125" t="s">
         <v>46</v>
       </c>
-      <c r="F125" t="s">
-        <v>74</v>
-      </c>
-      <c r="G125" t="s">
-        <v>47</v>
-      </c>
       <c r="H125" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I125" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
@@ -4513,22 +4523,22 @@
         <v>10</v>
       </c>
       <c r="B126" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D126" t="s">
         <v>20</v>
       </c>
       <c r="E126" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I126" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
@@ -4536,19 +4546,19 @@
         <v>10</v>
       </c>
       <c r="B127" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D127" t="s">
         <v>20</v>
       </c>
       <c r="E127" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F127" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H127" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I127" t="s">
         <v>20</v>
@@ -4559,13 +4569,13 @@
         <v>10</v>
       </c>
       <c r="B128" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D128" t="s">
         <v>20</v>
       </c>
       <c r="E128" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F128" t="s">
         <v>13</v>
@@ -4582,7 +4592,10 @@
         <v>10</v>
       </c>
       <c r="B129" t="s">
-        <v>69</v>
+        <v>78</v>
+      </c>
+      <c r="C129" t="b">
+        <v>1</v>
       </c>
       <c r="D129" t="s">
         <v>20</v>
@@ -4591,16 +4604,16 @@
         <v>21</v>
       </c>
       <c r="F129" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G129" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="H129" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I129" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J129" t="s">
         <v>17</v>
@@ -4611,7 +4624,7 @@
         <v>10</v>
       </c>
       <c r="B130" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D130" t="s">
         <v>20</v>
@@ -4620,7 +4633,7 @@
         <v>23</v>
       </c>
       <c r="F130" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G130" t="s">
         <v>24</v>
@@ -4631,22 +4644,22 @@
         <v>10</v>
       </c>
       <c r="B131" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D131" t="s">
         <v>20</v>
       </c>
       <c r="E131" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F131" t="s">
+        <v>25</v>
+      </c>
+      <c r="H131" t="s">
+        <v>25</v>
+      </c>
+      <c r="I131" t="s">
         <v>26</v>
-      </c>
-      <c r="H131" t="s">
-        <v>26</v>
-      </c>
-      <c r="I131" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
@@ -4654,22 +4667,22 @@
         <v>10</v>
       </c>
       <c r="B132" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D132" t="s">
         <v>20</v>
       </c>
       <c r="E132" t="s">
+        <v>27</v>
+      </c>
+      <c r="F132" t="s">
+        <v>25</v>
+      </c>
+      <c r="H132" t="s">
+        <v>25</v>
+      </c>
+      <c r="I132" t="s">
         <v>28</v>
-      </c>
-      <c r="F132" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" t="s">
-        <v>26</v>
-      </c>
-      <c r="I132" t="s">
-        <v>29</v>
       </c>
       <c r="J132" t="s">
         <v>17</v>
@@ -4680,22 +4693,22 @@
         <v>10</v>
       </c>
       <c r="B133" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D133" t="s">
         <v>20</v>
       </c>
       <c r="E133" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F133" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -4703,7 +4716,7 @@
         <v>10</v>
       </c>
       <c r="B134" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C134" t="b">
         <v>1</v>
@@ -4712,13 +4725,13 @@
         <v>20</v>
       </c>
       <c r="E134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F134" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G134" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
@@ -4726,19 +4739,19 @@
         <v>10</v>
       </c>
       <c r="B135" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D135" t="s">
         <v>20</v>
       </c>
       <c r="E135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F135" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H135" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I135" t="s">
         <v>17</v>
@@ -4749,19 +4762,19 @@
         <v>10</v>
       </c>
       <c r="B136" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D136" t="s">
         <v>20</v>
       </c>
       <c r="E136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F136" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H136" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I136" t="s">
         <v>17</v>
@@ -4772,19 +4785,19 @@
         <v>10</v>
       </c>
       <c r="B137" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D137" t="s">
         <v>20</v>
       </c>
       <c r="E137" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I137" t="s">
         <v>17</v>
@@ -4798,19 +4811,19 @@
         <v>10</v>
       </c>
       <c r="B138" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D138" t="s">
         <v>20</v>
       </c>
       <c r="E138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G138" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -4818,19 +4831,19 @@
         <v>10</v>
       </c>
       <c r="B139" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D139" t="s">
         <v>20</v>
       </c>
       <c r="E139" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F139" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H139" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I139" t="s">
         <v>17</v>
@@ -4841,25 +4854,25 @@
         <v>10</v>
       </c>
       <c r="B140" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D140" t="s">
         <v>20</v>
       </c>
       <c r="E140" t="s">
+        <v>45</v>
+      </c>
+      <c r="F140" t="s">
+        <v>73</v>
+      </c>
+      <c r="G140" t="s">
         <v>46</v>
       </c>
-      <c r="F140" t="s">
-        <v>74</v>
-      </c>
-      <c r="G140" t="s">
-        <v>47</v>
-      </c>
       <c r="H140" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I140" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
@@ -4867,22 +4880,22 @@
         <v>10</v>
       </c>
       <c r="B141" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D141" t="s">
         <v>20</v>
       </c>
       <c r="E141" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I141" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
@@ -4890,19 +4903,19 @@
         <v>10</v>
       </c>
       <c r="B142" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D142" t="s">
         <v>20</v>
       </c>
       <c r="E142" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F142" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H142" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I142" t="s">
         <v>20</v>
@@ -4913,13 +4926,13 @@
         <v>10</v>
       </c>
       <c r="B143" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D143" t="s">
         <v>20</v>
       </c>
       <c r="E143" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F143" t="s">
         <v>13</v>
@@ -4936,10 +4949,7 @@
         <v>10</v>
       </c>
       <c r="B144" t="s">
-        <v>80</v>
-      </c>
-      <c r="C144" t="b">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D144" t="s">
         <v>20</v>
@@ -4948,16 +4958,16 @@
         <v>21</v>
       </c>
       <c r="F144" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="H144" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I144" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J144" t="s">
         <v>17</v>
@@ -4968,7 +4978,7 @@
         <v>10</v>
       </c>
       <c r="B145" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D145" t="s">
         <v>20</v>
@@ -4977,13 +4987,13 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G145" t="s">
         <v>24</v>
       </c>
       <c r="J145" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -4991,22 +5001,22 @@
         <v>10</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D146" t="s">
         <v>20</v>
       </c>
       <c r="E146" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I146" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
@@ -5014,22 +5024,22 @@
         <v>10</v>
       </c>
       <c r="B147" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D147" t="s">
         <v>20</v>
       </c>
       <c r="E147" t="s">
+        <v>27</v>
+      </c>
+      <c r="F147" t="s">
+        <v>25</v>
+      </c>
+      <c r="H147" t="s">
+        <v>25</v>
+      </c>
+      <c r="I147" t="s">
         <v>28</v>
-      </c>
-      <c r="F147" t="s">
-        <v>26</v>
-      </c>
-      <c r="H147" t="s">
-        <v>26</v>
-      </c>
-      <c r="I147" t="s">
-        <v>29</v>
       </c>
       <c r="J147" t="s">
         <v>17</v>
@@ -5040,19 +5050,19 @@
         <v>10</v>
       </c>
       <c r="B148" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D148" t="s">
         <v>20</v>
       </c>
       <c r="E148" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148" t="s">
         <v>30</v>
       </c>
-      <c r="F148" t="s">
-        <v>31</v>
-      </c>
       <c r="G148" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J148" t="s">
         <v>17</v>
@@ -5063,19 +5073,19 @@
         <v>10</v>
       </c>
       <c r="B149" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D149" t="s">
         <v>20</v>
       </c>
       <c r="E149" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F149" t="s">
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
@@ -5083,19 +5093,19 @@
         <v>10</v>
       </c>
       <c r="B150" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D150" t="s">
         <v>20</v>
       </c>
       <c r="E150" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I150" t="s">
         <v>17</v>
@@ -5106,19 +5116,19 @@
         <v>10</v>
       </c>
       <c r="B151" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D151" t="s">
         <v>20</v>
       </c>
       <c r="E151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F151" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H151" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I151" t="s">
         <v>17</v>
@@ -5129,19 +5139,19 @@
         <v>10</v>
       </c>
       <c r="B152" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D152" t="s">
         <v>20</v>
       </c>
       <c r="E152" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F152" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H152" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I152" t="s">
         <v>17</v>
@@ -5155,19 +5165,19 @@
         <v>10</v>
       </c>
       <c r="B153" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D153" t="s">
         <v>20</v>
       </c>
       <c r="E153" t="s">
+        <v>41</v>
+      </c>
+      <c r="F153" t="s">
+        <v>41</v>
+      </c>
+      <c r="G153" t="s">
         <v>42</v>
-      </c>
-      <c r="F153" t="s">
-        <v>42</v>
-      </c>
-      <c r="G153" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.2">
@@ -5175,19 +5185,19 @@
         <v>10</v>
       </c>
       <c r="B154" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D154" t="s">
         <v>20</v>
       </c>
       <c r="E154" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I154" t="s">
         <v>17</v>
@@ -5198,25 +5208,25 @@
         <v>10</v>
       </c>
       <c r="B155" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D155" t="s">
         <v>20</v>
       </c>
       <c r="E155" t="s">
+        <v>45</v>
+      </c>
+      <c r="F155" t="s">
+        <v>73</v>
+      </c>
+      <c r="G155" t="s">
         <v>46</v>
       </c>
-      <c r="F155" t="s">
-        <v>74</v>
-      </c>
-      <c r="G155" t="s">
-        <v>47</v>
-      </c>
       <c r="H155" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I155" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.2">
@@ -5224,22 +5234,22 @@
         <v>10</v>
       </c>
       <c r="B156" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D156" t="s">
         <v>20</v>
       </c>
       <c r="E156" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F156" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H156" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I156" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.2">
@@ -5247,19 +5257,19 @@
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D157" t="s">
         <v>20</v>
       </c>
       <c r="E157" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F157" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H157" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I157" t="s">
         <v>20</v>
@@ -5270,13 +5280,13 @@
         <v>10</v>
       </c>
       <c r="B158" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D158" t="s">
         <v>20</v>
       </c>
       <c r="E158" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F158" t="s">
         <v>13</v>
@@ -5293,7 +5303,7 @@
         <v>10</v>
       </c>
       <c r="B159" t="s">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="D159" t="s">
         <v>20</v>
@@ -5302,16 +5312,16 @@
         <v>21</v>
       </c>
       <c r="F159" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G159" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="H159" t="s">
-        <v>176</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>83</v>
+        <v>175</v>
+      </c>
+      <c r="I159" t="s">
+        <v>82</v>
       </c>
       <c r="J159" t="s">
         <v>17</v>
@@ -5322,7 +5332,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D160" t="s">
         <v>20</v>
@@ -5331,10 +5341,10 @@
         <v>23</v>
       </c>
       <c r="F160" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G160" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.2">
@@ -5342,22 +5352,22 @@
         <v>10</v>
       </c>
       <c r="B161" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D161" t="s">
         <v>20</v>
       </c>
       <c r="E161" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="F161" t="s">
+        <v>25</v>
+      </c>
+      <c r="H161" t="s">
+        <v>25</v>
+      </c>
+      <c r="I161" t="s">
         <v>26</v>
-      </c>
-      <c r="H161" t="s">
-        <v>26</v>
-      </c>
-      <c r="I161" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -5365,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="B162" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C162" t="b">
         <v>1</v>
@@ -5374,13 +5384,13 @@
         <v>20</v>
       </c>
       <c r="E162" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F162" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G162" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
@@ -5391,19 +5401,19 @@
         <v>10</v>
       </c>
       <c r="B163" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D163" t="s">
         <v>20</v>
       </c>
       <c r="E163" t="s">
+        <v>29</v>
+      </c>
+      <c r="F163" t="s">
         <v>30</v>
       </c>
-      <c r="F163" t="s">
-        <v>31</v>
-      </c>
       <c r="G163" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.2">
@@ -5411,19 +5421,19 @@
         <v>10</v>
       </c>
       <c r="B164" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D164" t="s">
         <v>20</v>
       </c>
       <c r="E164" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F164" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G164" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.2">
@@ -5431,19 +5441,19 @@
         <v>10</v>
       </c>
       <c r="B165" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D165" t="s">
         <v>20</v>
       </c>
       <c r="E165" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F165" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H165" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I165" t="s">
         <v>17</v>
@@ -5454,19 +5464,19 @@
         <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D166" t="s">
         <v>20</v>
       </c>
       <c r="E166" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F166" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H166" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I166" t="s">
         <v>17</v>
@@ -5477,19 +5487,19 @@
         <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D167" t="s">
         <v>20</v>
       </c>
       <c r="E167" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F167" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H167" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I167" t="s">
         <v>17</v>
@@ -5500,19 +5510,19 @@
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D168" t="s">
         <v>20</v>
       </c>
       <c r="E168" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F168" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H168" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I168" t="s">
         <v>17</v>
@@ -5523,19 +5533,19 @@
         <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D169" t="s">
         <v>20</v>
       </c>
       <c r="E169" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F169" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H169" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I169" t="s">
         <v>17</v>
@@ -5546,25 +5556,25 @@
         <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D170" t="s">
         <v>20</v>
       </c>
       <c r="E170" t="s">
+        <v>45</v>
+      </c>
+      <c r="F170" t="s">
+        <v>73</v>
+      </c>
+      <c r="G170" t="s">
         <v>46</v>
       </c>
-      <c r="F170" t="s">
-        <v>74</v>
-      </c>
-      <c r="G170" t="s">
-        <v>47</v>
-      </c>
       <c r="H170" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I170" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.2">
@@ -5572,22 +5582,22 @@
         <v>10</v>
       </c>
       <c r="B171" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
       </c>
       <c r="E171" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F171" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H171" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I171" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.2">
@@ -5595,22 +5605,22 @@
         <v>10</v>
       </c>
       <c r="B172" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D172" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E172" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F172" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H172" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I172" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.2">
@@ -5618,13 +5628,13 @@
         <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D173" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F173" t="s">
         <v>13</v>
@@ -5638,25 +5648,25 @@
         <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D174" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F174" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G174" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H174" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I174" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.2">
@@ -5664,22 +5674,22 @@
         <v>10</v>
       </c>
       <c r="B175" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C175" t="b">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
       </c>
       <c r="G175" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
@@ -5687,19 +5697,19 @@
         <v>10</v>
       </c>
       <c r="B176" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D176" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F176" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G176" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
@@ -5707,22 +5717,22 @@
         <v>10</v>
       </c>
       <c r="B177" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D177" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E177" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F177" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G177" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K177" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
@@ -5730,19 +5740,19 @@
         <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D178" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E178" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F178" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G178" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
@@ -5750,19 +5760,19 @@
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D179" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E179" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F179" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G179" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
@@ -5770,19 +5780,19 @@
         <v>10</v>
       </c>
       <c r="B180" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D180" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E180" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F180" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H180" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.2">
@@ -5790,19 +5800,19 @@
         <v>10</v>
       </c>
       <c r="B181" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D181" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E181" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F181" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H181" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.2">
@@ -5810,19 +5820,19 @@
         <v>10</v>
       </c>
       <c r="B182" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D182" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E182" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F182" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H182" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.2">
@@ -5830,19 +5840,19 @@
         <v>10</v>
       </c>
       <c r="B183" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D183" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E183" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F183" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H183" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.2">
@@ -5850,19 +5860,19 @@
         <v>10</v>
       </c>
       <c r="B184" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D184" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E184" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F184" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H184" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.2">
@@ -5870,19 +5880,19 @@
         <v>10</v>
       </c>
       <c r="B185" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D185" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E185" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F185" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H185" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
@@ -5890,19 +5900,19 @@
         <v>10</v>
       </c>
       <c r="B186" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D186" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E186" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F186" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H186" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.2">
@@ -5910,22 +5920,22 @@
         <v>10</v>
       </c>
       <c r="B187" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D187" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E187" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F187" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H187" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I187" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
@@ -5933,13 +5943,13 @@
         <v>10</v>
       </c>
       <c r="B188" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D188" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F188" t="s">
         <v>13</v>
@@ -5953,31 +5963,31 @@
         <v>10</v>
       </c>
       <c r="B189" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D189" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F189" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G189" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H189" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I189" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J189" t="s">
         <v>17</v>
       </c>
       <c r="K189" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
@@ -5985,19 +5995,19 @@
         <v>10</v>
       </c>
       <c r="B190" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D190" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F190" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G190" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.2">
@@ -6005,19 +6015,19 @@
         <v>10</v>
       </c>
       <c r="B191" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D191" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F191" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H191" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I191">
         <v>-999</v>
@@ -6028,19 +6038,19 @@
         <v>10</v>
       </c>
       <c r="B192" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D192" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F192" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H192" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I192" t="s">
         <v>17</v>
@@ -6051,19 +6061,19 @@
         <v>10</v>
       </c>
       <c r="B193" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D193" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F193" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H193" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I193" t="s">
         <v>17</v>
@@ -6074,22 +6084,22 @@
         <v>10</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D194" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E194" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F194" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H194" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.2">
@@ -6097,13 +6107,13 @@
         <v>10</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D195" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -6117,13 +6127,13 @@
         <v>10</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D196" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F196" t="s">
         <v>13</v>
@@ -6132,10 +6142,10 @@
         <v>14</v>
       </c>
       <c r="H196" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I196" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.2">
@@ -6143,22 +6153,22 @@
         <v>10</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D197" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F197" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H197" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I197" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.2">
@@ -6166,28 +6176,28 @@
         <v>10</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C198" t="b">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F198" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G198" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H198" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I198" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.2">
@@ -6195,19 +6205,19 @@
         <v>10</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D199" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I199">
         <v>-999</v>
@@ -6218,19 +6228,19 @@
         <v>10</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D200" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F200" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H200" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I200">
         <v>-999</v>
@@ -6244,19 +6254,19 @@
         <v>10</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D201" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F201" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G201" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.2">
@@ -6264,19 +6274,19 @@
         <v>10</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D202" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E202" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F202" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H202" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.2">
@@ -6284,19 +6294,19 @@
         <v>10</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D203" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E203" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F203" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H203" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.2">
@@ -6304,19 +6314,19 @@
         <v>10</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D204" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F204" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H204" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I204" t="s">
         <v>17</v>
@@ -6327,19 +6337,19 @@
         <v>10</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D205" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F205" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H205" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.2">
@@ -6347,22 +6357,22 @@
         <v>10</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D206" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E206" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F206" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H206" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I206" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.2">
@@ -6370,19 +6380,19 @@
         <v>10</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D207" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E207" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F207" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H207" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.2">
@@ -6390,19 +6400,19 @@
         <v>10</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D208" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E208" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F208" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H208" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.2">
@@ -6410,19 +6420,19 @@
         <v>10</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D209" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E209" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F209" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H209" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.2">
@@ -6430,22 +6440,22 @@
         <v>10</v>
       </c>
       <c r="B210" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D210" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E210" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F210" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H210" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I210" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.2">
@@ -6453,13 +6463,13 @@
         <v>10</v>
       </c>
       <c r="B211" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D211" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F211" t="s">
         <v>13</v>
@@ -6473,13 +6483,13 @@
         <v>10</v>
       </c>
       <c r="B212" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D212" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F212" t="s">
         <v>13</v>
@@ -6488,10 +6498,10 @@
         <v>14</v>
       </c>
       <c r="H212" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I212" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.2">
@@ -6499,22 +6509,22 @@
         <v>10</v>
       </c>
       <c r="B213" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D213" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F213" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H213" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I213" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.2">
@@ -6522,22 +6532,22 @@
         <v>10</v>
       </c>
       <c r="B214" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C214" t="b">
         <v>1</v>
       </c>
       <c r="D214" t="s">
+        <v>115</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E214" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="F214" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.2">
@@ -6545,19 +6555,19 @@
         <v>10</v>
       </c>
       <c r="B215" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D215" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F215" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H215" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I215">
         <v>-999</v>
@@ -6568,19 +6578,19 @@
         <v>10</v>
       </c>
       <c r="B216" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D216" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F216" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H216" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I216">
         <v>-999</v>
@@ -6591,22 +6601,22 @@
         <v>10</v>
       </c>
       <c r="B217" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D217" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E217" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F217" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H217" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I217" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.2">
@@ -6614,13 +6624,13 @@
         <v>10</v>
       </c>
       <c r="B218" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D218" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F218" t="s">
         <v>13</v>
@@ -6634,13 +6644,13 @@
         <v>10</v>
       </c>
       <c r="B219" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D219" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F219" t="s">
         <v>13</v>
@@ -6649,10 +6659,10 @@
         <v>14</v>
       </c>
       <c r="H219" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I219" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.2">
@@ -6660,25 +6670,25 @@
         <v>10</v>
       </c>
       <c r="B220" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D220" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F220" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H220" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I220" t="s">
+        <v>187</v>
+      </c>
+      <c r="J220" t="s">
         <v>189</v>
-      </c>
-      <c r="J220" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.2">
@@ -6686,25 +6696,25 @@
         <v>10</v>
       </c>
       <c r="B221" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C221" t="b">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F221" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G221" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J221" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.2">
@@ -6712,19 +6722,19 @@
         <v>10</v>
       </c>
       <c r="B222" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D222" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F222" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G222" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J222">
         <v>-999</v>
@@ -6735,19 +6745,19 @@
         <v>10</v>
       </c>
       <c r="B223" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D223" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F223" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G223" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J223">
         <v>-999</v>
@@ -6758,19 +6768,19 @@
         <v>10</v>
       </c>
       <c r="B224" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D224" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F224" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H224" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I224" t="s">
         <v>17</v>
@@ -6781,22 +6791,22 @@
         <v>10</v>
       </c>
       <c r="B225" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D225" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G225" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I225" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
@@ -6804,22 +6814,22 @@
         <v>10</v>
       </c>
       <c r="B226" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D226" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E226" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F226" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H226" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I226" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
@@ -6827,13 +6837,13 @@
         <v>10</v>
       </c>
       <c r="B227" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D227" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F227" t="s">
         <v>13</v>
@@ -6847,13 +6857,13 @@
         <v>10</v>
       </c>
       <c r="B228" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D228" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F228" t="s">
         <v>13</v>
@@ -6862,10 +6872,10 @@
         <v>14</v>
       </c>
       <c r="H228" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I228" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
@@ -6873,22 +6883,22 @@
         <v>10</v>
       </c>
       <c r="B229" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D229" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F229" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H229" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I229" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
@@ -6896,22 +6906,22 @@
         <v>10</v>
       </c>
       <c r="B230" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D230" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F230" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H230" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I230" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
@@ -6919,19 +6929,19 @@
         <v>10</v>
       </c>
       <c r="B231" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D231" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F231" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H231" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I231">
         <v>-999</v>
@@ -6942,19 +6952,19 @@
         <v>10</v>
       </c>
       <c r="B232" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D232" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F232" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H232" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I232">
         <v>-999</v>
@@ -6965,22 +6975,22 @@
         <v>10</v>
       </c>
       <c r="B233" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C233" t="b">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F233" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G233" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
@@ -6988,19 +6998,19 @@
         <v>10</v>
       </c>
       <c r="B234" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D234" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E234" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F234" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H234" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
@@ -7008,19 +7018,19 @@
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D235" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E235" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F235" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H235" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
@@ -7028,19 +7038,19 @@
         <v>10</v>
       </c>
       <c r="B236" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D236" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E236" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F236" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H236" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
@@ -7048,19 +7058,19 @@
         <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D237" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E237" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F237" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H237" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
@@ -7068,19 +7078,19 @@
         <v>10</v>
       </c>
       <c r="B238" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D238" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E238" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F238" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H238" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
@@ -7088,19 +7098,19 @@
         <v>10</v>
       </c>
       <c r="B239" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D239" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E239" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F239" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H239" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
@@ -7108,19 +7118,19 @@
         <v>10</v>
       </c>
       <c r="B240" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D240" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E240" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F240" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H240" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
@@ -7128,22 +7138,22 @@
         <v>10</v>
       </c>
       <c r="B241" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D241" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E241" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F241" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H241" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I241" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -7151,13 +7161,13 @@
         <v>10</v>
       </c>
       <c r="B242" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D242" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F242" t="s">
         <v>13</v>
@@ -7171,13 +7181,13 @@
         <v>10</v>
       </c>
       <c r="B243" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D243" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F243" t="s">
         <v>13</v>
@@ -7186,10 +7196,10 @@
         <v>14</v>
       </c>
       <c r="H243" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I243" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
@@ -7197,22 +7207,22 @@
         <v>10</v>
       </c>
       <c r="B244" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D244" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F244" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H244" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I244" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
@@ -7220,22 +7230,22 @@
         <v>10</v>
       </c>
       <c r="B245" t="s">
+        <v>196</v>
+      </c>
+      <c r="D245" t="s">
+        <v>103</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F245" t="s">
+        <v>25</v>
+      </c>
+      <c r="H245" t="s">
+        <v>25</v>
+      </c>
+      <c r="I245" t="s">
         <v>198</v>
-      </c>
-      <c r="D245" t="s">
-        <v>105</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F245" t="s">
-        <v>26</v>
-      </c>
-      <c r="H245" t="s">
-        <v>26</v>
-      </c>
-      <c r="I245" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -7243,19 +7253,19 @@
         <v>10</v>
       </c>
       <c r="B246" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D246" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F246" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H246" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I246">
         <v>-999</v>
@@ -7266,19 +7276,19 @@
         <v>10</v>
       </c>
       <c r="B247" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D247" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F247" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H247" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I247">
         <v>-999</v>
@@ -7289,22 +7299,22 @@
         <v>10</v>
       </c>
       <c r="B248" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C248" t="b">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F248" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G248" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
@@ -7312,19 +7322,19 @@
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D249" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E249" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F249" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H249" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
@@ -7332,19 +7342,19 @@
         <v>10</v>
       </c>
       <c r="B250" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D250" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E250" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F250" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H250" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
@@ -7352,19 +7362,19 @@
         <v>10</v>
       </c>
       <c r="B251" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D251" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E251" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F251" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H251" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
@@ -7372,19 +7382,19 @@
         <v>10</v>
       </c>
       <c r="B252" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D252" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E252" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F252" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H252" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
@@ -7392,19 +7402,19 @@
         <v>10</v>
       </c>
       <c r="B253" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D253" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E253" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F253" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H253" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
@@ -7412,19 +7422,19 @@
         <v>10</v>
       </c>
       <c r="B254" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D254" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E254" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F254" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H254" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
@@ -7432,19 +7442,19 @@
         <v>10</v>
       </c>
       <c r="B255" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D255" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E255" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F255" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H255" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
@@ -7452,22 +7462,22 @@
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D256" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E256" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F256" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H256" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I256" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
@@ -7475,13 +7485,13 @@
         <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D257" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F257" t="s">
         <v>13</v>
@@ -7495,13 +7505,13 @@
         <v>10</v>
       </c>
       <c r="B258" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D258" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F258" t="s">
         <v>13</v>
@@ -7510,10 +7520,10 @@
         <v>14</v>
       </c>
       <c r="H258" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I258" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
@@ -7521,22 +7531,22 @@
         <v>10</v>
       </c>
       <c r="B259" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D259" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F259" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H259" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I259" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
@@ -7544,22 +7554,22 @@
         <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D260" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F260" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H260" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I260" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
@@ -7567,19 +7577,19 @@
         <v>10</v>
       </c>
       <c r="B261" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D261" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F261" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H261" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I261">
         <v>-999</v>
@@ -7590,19 +7600,19 @@
         <v>10</v>
       </c>
       <c r="B262" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D262" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F262" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H262" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I262">
         <v>-999</v>
@@ -7613,22 +7623,22 @@
         <v>10</v>
       </c>
       <c r="B263" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C263" t="b">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F263" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G263" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
@@ -7636,19 +7646,19 @@
         <v>10</v>
       </c>
       <c r="B264" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D264" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E264" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F264" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H264" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
@@ -7656,19 +7666,19 @@
         <v>10</v>
       </c>
       <c r="B265" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D265" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E265" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F265" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H265" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
@@ -7676,19 +7686,19 @@
         <v>10</v>
       </c>
       <c r="B266" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D266" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E266" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F266" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H266" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
@@ -7696,19 +7706,19 @@
         <v>10</v>
       </c>
       <c r="B267" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D267" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E267" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F267" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H267" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
@@ -7716,19 +7726,19 @@
         <v>10</v>
       </c>
       <c r="B268" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D268" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E268" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F268" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H268" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
@@ -7736,19 +7746,19 @@
         <v>10</v>
       </c>
       <c r="B269" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D269" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E269" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F269" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H269" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
@@ -7756,19 +7766,19 @@
         <v>10</v>
       </c>
       <c r="B270" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D270" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E270" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F270" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H270" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
@@ -7776,22 +7786,22 @@
         <v>10</v>
       </c>
       <c r="B271" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D271" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E271" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F271" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H271" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I271" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
@@ -7799,13 +7809,13 @@
         <v>10</v>
       </c>
       <c r="B272" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D272" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F272" t="s">
         <v>13</v>
@@ -7819,13 +7829,13 @@
         <v>10</v>
       </c>
       <c r="B273" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D273" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F273" t="s">
         <v>13</v>
@@ -7834,10 +7844,10 @@
         <v>14</v>
       </c>
       <c r="H273" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I273" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
@@ -7845,22 +7855,22 @@
         <v>10</v>
       </c>
       <c r="B274" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D274" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F274" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H274" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I274" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
@@ -7868,22 +7878,22 @@
         <v>10</v>
       </c>
       <c r="B275" t="s">
+        <v>203</v>
+      </c>
+      <c r="D275" t="s">
+        <v>103</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F275" t="s">
+        <v>25</v>
+      </c>
+      <c r="H275" t="s">
+        <v>25</v>
+      </c>
+      <c r="I275" t="s">
         <v>205</v>
-      </c>
-      <c r="D275" t="s">
-        <v>105</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F275" t="s">
-        <v>26</v>
-      </c>
-      <c r="H275" t="s">
-        <v>26</v>
-      </c>
-      <c r="I275" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
@@ -7891,19 +7901,19 @@
         <v>10</v>
       </c>
       <c r="B276" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D276" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F276" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H276" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I276">
         <v>-999</v>
@@ -7914,19 +7924,19 @@
         <v>10</v>
       </c>
       <c r="B277" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D277" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F277" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H277" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I277">
         <v>-999</v>
@@ -7937,22 +7947,22 @@
         <v>10</v>
       </c>
       <c r="B278" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C278" t="b">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F278" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G278" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
@@ -7960,19 +7970,19 @@
         <v>10</v>
       </c>
       <c r="B279" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D279" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E279" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F279" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H279" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.2">
@@ -7980,19 +7990,19 @@
         <v>10</v>
       </c>
       <c r="B280" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D280" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E280" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F280" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H280" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.2">
@@ -8000,19 +8010,19 @@
         <v>10</v>
       </c>
       <c r="B281" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D281" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E281" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F281" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H281" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.2">
@@ -8020,19 +8030,19 @@
         <v>10</v>
       </c>
       <c r="B282" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D282" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E282" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F282" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H282" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.2">
@@ -8040,19 +8050,19 @@
         <v>10</v>
       </c>
       <c r="B283" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D283" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E283" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F283" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H283" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.2">
@@ -8060,19 +8070,19 @@
         <v>10</v>
       </c>
       <c r="B284" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D284" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E284" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F284" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H284" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.2">
@@ -8080,19 +8090,19 @@
         <v>10</v>
       </c>
       <c r="B285" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D285" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E285" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F285" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H285" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.2">
@@ -8100,22 +8110,22 @@
         <v>10</v>
       </c>
       <c r="B286" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D286" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E286" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F286" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H286" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I286" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
@@ -8123,13 +8133,13 @@
         <v>10</v>
       </c>
       <c r="B287" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D287" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F287" t="s">
         <v>13</v>
@@ -8143,19 +8153,19 @@
         <v>10</v>
       </c>
       <c r="B288" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D288" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
@@ -8165,22 +8175,22 @@
         <v>10</v>
       </c>
       <c r="B289" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D289" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H289" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I289" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -8188,19 +8198,19 @@
         <v>10</v>
       </c>
       <c r="B290" t="s">
+        <v>207</v>
+      </c>
+      <c r="D290" t="s">
+        <v>103</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F290" t="s">
+        <v>211</v>
+      </c>
+      <c r="G290" t="s">
         <v>209</v>
-      </c>
-      <c r="D290" t="s">
-        <v>105</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F290" t="s">
-        <v>213</v>
-      </c>
-      <c r="G290" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -8208,19 +8218,19 @@
         <v>10</v>
       </c>
       <c r="B291" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D291" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F291" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H291" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I291">
         <v>-999</v>
@@ -8231,19 +8241,19 @@
         <v>10</v>
       </c>
       <c r="B292" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D292" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F292" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H292" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I292">
         <v>-999</v>
@@ -8254,22 +8264,22 @@
         <v>10</v>
       </c>
       <c r="B293" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C293" t="b">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G293" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
@@ -8277,19 +8287,19 @@
         <v>10</v>
       </c>
       <c r="B294" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D294" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E294" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F294" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H294" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
@@ -8297,19 +8307,19 @@
         <v>10</v>
       </c>
       <c r="B295" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D295" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E295" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F295" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H295" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
@@ -8317,19 +8327,19 @@
         <v>10</v>
       </c>
       <c r="B296" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D296" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E296" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F296" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H296" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
@@ -8337,19 +8347,19 @@
         <v>10</v>
       </c>
       <c r="B297" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D297" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E297" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F297" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H297" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
@@ -8357,19 +8367,19 @@
         <v>10</v>
       </c>
       <c r="B298" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D298" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E298" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F298" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H298" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
@@ -8377,19 +8387,19 @@
         <v>10</v>
       </c>
       <c r="B299" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D299" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E299" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F299" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H299" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
@@ -8397,23 +8407,258 @@
         <v>10</v>
       </c>
       <c r="B300" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D300" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E300" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F300" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H300" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>10</v>
+      </c>
+      <c r="B301" t="s">
+        <v>49</v>
+      </c>
+      <c r="C301" t="b">
+        <v>1</v>
+      </c>
+      <c r="D301" t="s">
+        <v>20</v>
+      </c>
+      <c r="E301" t="s">
+        <v>219</v>
+      </c>
+      <c r="F301" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G301" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>10</v>
+      </c>
+      <c r="B302" t="s">
+        <v>66</v>
+      </c>
+      <c r="D302" t="s">
+        <v>20</v>
+      </c>
+      <c r="E302" t="s">
+        <v>219</v>
+      </c>
+      <c r="F302" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G302" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>10</v>
+      </c>
+      <c r="B303" t="s">
+        <v>58</v>
+      </c>
+      <c r="D303" t="s">
+        <v>20</v>
+      </c>
+      <c r="E303" t="s">
+        <v>219</v>
+      </c>
+      <c r="F303" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G303" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>10</v>
+      </c>
+      <c r="B304" t="s">
+        <v>78</v>
+      </c>
+      <c r="C304" t="b">
+        <v>1</v>
+      </c>
+      <c r="D304" t="s">
+        <v>20</v>
+      </c>
+      <c r="E304" t="s">
+        <v>219</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G304" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>10</v>
+      </c>
+      <c r="B305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>20</v>
+      </c>
+      <c r="E305" t="s">
+        <v>219</v>
+      </c>
+      <c r="F305" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G305" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>10</v>
+      </c>
+      <c r="B306" t="s">
+        <v>62</v>
+      </c>
+      <c r="D306" t="s">
+        <v>20</v>
+      </c>
+      <c r="E306" t="s">
+        <v>219</v>
+      </c>
+      <c r="F306" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G306" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>10</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C307" t="b">
+        <v>1</v>
+      </c>
+      <c r="D307" t="s">
+        <v>20</v>
+      </c>
+      <c r="E307" t="s">
+        <v>219</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G307" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>10</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D308" t="s">
+        <v>20</v>
+      </c>
+      <c r="E308" t="s">
+        <v>219</v>
+      </c>
+      <c r="F308" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G308" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>10</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D309" t="s">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>219</v>
+      </c>
+      <c r="F309" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G309" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>10</v>
+      </c>
+      <c r="B310" t="s">
+        <v>153</v>
+      </c>
+      <c r="D310" t="s">
+        <v>20</v>
+      </c>
+      <c r="E310" t="s">
+        <v>219</v>
+      </c>
+      <c r="F310" t="s">
+        <v>25</v>
+      </c>
+      <c r="H310" t="s">
+        <v>25</v>
+      </c>
+      <c r="I310" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>10</v>
+      </c>
+      <c r="B311" t="s">
+        <v>19</v>
+      </c>
+      <c r="D311" t="s">
+        <v>20</v>
+      </c>
+      <c r="E311" t="s">
+        <v>219</v>
+      </c>
+      <c r="F311" t="s">
+        <v>25</v>
+      </c>
+      <c r="H311" t="s">
+        <v>25</v>
+      </c>
+      <c r="I311" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K300" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}"/>
+  <autoFilter ref="A1:K311" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -8432,7 +8677,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -8440,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -8448,7 +8693,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -8456,7 +8701,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -8464,7 +8709,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -8472,7 +8717,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -8480,7 +8725,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -8488,7 +8733,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8496,7 +8741,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -8504,7 +8749,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09510FC5-1A98-714C-8771-D3198F641933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7279EC7-D9A7-D14B-B738-5A6BE7ED0484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="1620" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
+    <workbookView xWindow="-34420" yWindow="-6720" windowWidth="32640" windowHeight="20520" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="cog_rules" sheetId="1" r:id="rId1"/>
     <sheet name="key" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cog_rules!$A$1:$K$311</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cog_rules!$A$1:$K$305</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="218">
   <si>
     <t>source</t>
   </si>
@@ -439,24 +439,6 @@
   </si>
   <si>
     <t>age_at_event_free_survival_status</t>
-  </si>
-  <si>
-    <t>follow_up_category</t>
-  </si>
-  <si>
-    <t>follow_up_other</t>
-  </si>
-  <si>
-    <t>adverse_event</t>
-  </si>
-  <si>
-    <t>comorbidity</t>
-  </si>
-  <si>
-    <t>comorbidity_method_of_diagnosis</t>
-  </si>
-  <si>
-    <t>risk_factor</t>
   </si>
   <si>
     <t>cause_of_death</t>
@@ -1210,13 +1192,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1592,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
-  <dimension ref="A1:K311"/>
+  <dimension ref="A1:K305"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
@@ -1636,7 +1617,7 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1650,7 +1631,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -1739,7 +1720,7 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -1748,7 +1729,7 @@
         <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1762,7 +1743,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -1817,7 +1798,7 @@
         <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>81</v>
@@ -1840,7 +1821,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -1860,7 +1841,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -1918,7 +1899,7 @@
         <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -2101,7 +2082,7 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -2156,7 +2137,7 @@
         <v>51</v>
       </c>
       <c r="H24" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>81</v>
@@ -2179,7 +2160,7 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
@@ -2199,7 +2180,7 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -2237,7 +2218,7 @@
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -2326,7 +2307,7 @@
         <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -2372,7 +2353,7 @@
         <v>41</v>
       </c>
       <c r="G33" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -2452,7 +2433,7 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -2504,7 +2485,7 @@
         <v>51</v>
       </c>
       <c r="H39" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>81</v>
@@ -2527,7 +2508,7 @@
         <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
@@ -2544,7 +2525,7 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -2662,7 +2643,7 @@
         <v>35</v>
       </c>
       <c r="G46" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -2754,7 +2735,7 @@
         <v>72</v>
       </c>
       <c r="I50" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2791,7 +2772,7 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -2846,7 +2827,7 @@
         <v>22</v>
       </c>
       <c r="H54" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>81</v>
@@ -2869,10 +2850,10 @@
         <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G55" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="J55" t="s">
         <v>53</v>
@@ -2889,7 +2870,7 @@
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F56" t="s">
         <v>25</v>
@@ -2921,7 +2902,7 @@
         <v>35</v>
       </c>
       <c r="G57" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
@@ -2964,7 +2945,7 @@
         <v>35</v>
       </c>
       <c r="G59" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
@@ -3142,7 +3123,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F67" t="s">
         <v>25</v>
@@ -3182,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
@@ -3197,7 +3178,7 @@
         <v>22</v>
       </c>
       <c r="H69" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>81</v>
@@ -3220,10 +3201,10 @@
         <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G70" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
@@ -3237,7 +3218,7 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F71" t="s">
         <v>25</v>
@@ -3312,7 +3293,7 @@
         <v>35</v>
       </c>
       <c r="G74" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
@@ -3490,7 +3471,7 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F82" t="s">
         <v>25</v>
@@ -3529,7 +3510,7 @@
       <c r="A84" t="s">
         <v>10</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" t="s">
         <v>56</v>
       </c>
       <c r="C84" t="b">
@@ -3548,7 +3529,7 @@
         <v>22</v>
       </c>
       <c r="H84" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>81</v>
@@ -3571,10 +3552,10 @@
         <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G85" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
         <v>53</v>
@@ -3591,7 +3572,7 @@
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F86" t="s">
         <v>25</v>
@@ -3623,7 +3604,7 @@
         <v>35</v>
       </c>
       <c r="G87" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
@@ -3666,7 +3647,7 @@
         <v>35</v>
       </c>
       <c r="G89" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
@@ -3844,7 +3825,7 @@
         <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F97" t="s">
         <v>25</v>
@@ -3883,7 +3864,7 @@
       <c r="A99" t="s">
         <v>10</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" t="s">
         <v>63</v>
       </c>
       <c r="D99" t="s">
@@ -3899,7 +3880,7 @@
         <v>22</v>
       </c>
       <c r="H99" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>81</v>
@@ -3922,7 +3903,7 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G100" t="s">
         <v>24</v>
@@ -3939,7 +3920,7 @@
         <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
@@ -3997,7 +3978,7 @@
         <v>25</v>
       </c>
       <c r="I103" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -4066,7 +4047,7 @@
         <v>35</v>
       </c>
       <c r="G106" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -4201,7 +4182,7 @@
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F112" t="s">
         <v>25</v>
@@ -4240,7 +4221,7 @@
       <c r="A114" t="s">
         <v>10</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" t="s">
         <v>60</v>
       </c>
       <c r="D114" t="s">
@@ -4256,7 +4237,7 @@
         <v>22</v>
       </c>
       <c r="H114" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>81</v>
@@ -4279,7 +4260,7 @@
         <v>23</v>
       </c>
       <c r="F115" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -4299,7 +4280,7 @@
         <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F116" t="s">
         <v>25</v>
@@ -4357,7 +4338,7 @@
         <v>25</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -4472,7 +4453,7 @@
         <v>41</v>
       </c>
       <c r="G123" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
@@ -4552,7 +4533,7 @@
         <v>20</v>
       </c>
       <c r="E127" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F127" t="s">
         <v>25</v>
@@ -4607,10 +4588,10 @@
         <v>50</v>
       </c>
       <c r="G129" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H129" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I129" t="s">
         <v>82</v>
@@ -4633,7 +4614,7 @@
         <v>23</v>
       </c>
       <c r="F130" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G130" t="s">
         <v>24</v>
@@ -4650,7 +4631,7 @@
         <v>20</v>
       </c>
       <c r="E131" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F131" t="s">
         <v>25</v>
@@ -4708,7 +4689,7 @@
         <v>25</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -4823,7 +4804,7 @@
         <v>41</v>
       </c>
       <c r="G138" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -4909,7 +4890,7 @@
         <v>20</v>
       </c>
       <c r="E142" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F142" t="s">
         <v>25</v>
@@ -4961,10 +4942,10 @@
         <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H144" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I144" t="s">
         <v>82</v>
@@ -4987,7 +4968,7 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G145" t="s">
         <v>24</v>
@@ -5007,7 +4988,7 @@
         <v>20</v>
       </c>
       <c r="E146" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F146" t="s">
         <v>25</v>
@@ -5257,13 +5238,13 @@
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D157" t="s">
         <v>20</v>
       </c>
       <c r="E157" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F157" t="s">
         <v>25</v>
@@ -5280,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="B158" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D158" t="s">
         <v>20</v>
@@ -5315,10 +5296,10 @@
         <v>50</v>
       </c>
       <c r="G159" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H159" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I159" t="s">
         <v>82</v>
@@ -5332,7 +5313,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D160" t="s">
         <v>20</v>
@@ -5341,10 +5322,10 @@
         <v>23</v>
       </c>
       <c r="F160" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G160" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.2">
@@ -5352,13 +5333,13 @@
         <v>10</v>
       </c>
       <c r="B161" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D161" t="s">
         <v>20</v>
       </c>
       <c r="E161" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F161" t="s">
         <v>25</v>
@@ -5375,7 +5356,7 @@
         <v>10</v>
       </c>
       <c r="B162" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C162" t="b">
         <v>1</v>
@@ -5390,7 +5371,7 @@
         <v>35</v>
       </c>
       <c r="G162" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
@@ -5401,7 +5382,7 @@
         <v>10</v>
       </c>
       <c r="B163" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D163" t="s">
         <v>20</v>
@@ -5421,7 +5402,7 @@
         <v>10</v>
       </c>
       <c r="B164" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D164" t="s">
         <v>20</v>
@@ -5433,7 +5414,7 @@
         <v>35</v>
       </c>
       <c r="G164" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.2">
@@ -5441,7 +5422,7 @@
         <v>10</v>
       </c>
       <c r="B165" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D165" t="s">
         <v>20</v>
@@ -5464,7 +5445,7 @@
         <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D166" t="s">
         <v>20</v>
@@ -5487,7 +5468,7 @@
         <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D167" t="s">
         <v>20</v>
@@ -5510,7 +5491,7 @@
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D168" t="s">
         <v>20</v>
@@ -5533,7 +5514,7 @@
         <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D169" t="s">
         <v>20</v>
@@ -5556,7 +5537,7 @@
         <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D170" t="s">
         <v>20</v>
@@ -5582,7 +5563,7 @@
         <v>10</v>
       </c>
       <c r="B171" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
@@ -5605,13 +5586,13 @@
         <v>10</v>
       </c>
       <c r="B172" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D172" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E172" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F172" t="s">
         <v>25</v>
@@ -5620,7 +5601,7 @@
         <v>25</v>
       </c>
       <c r="I172" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.2">
@@ -5628,10 +5609,10 @@
         <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D173" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>71</v>
@@ -5648,10 +5629,10 @@
         <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D174" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>128</v>
@@ -5660,13 +5641,13 @@
         <v>73</v>
       </c>
       <c r="G174" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H174" t="s">
         <v>80</v>
       </c>
       <c r="I174" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.2">
@@ -5674,13 +5655,13 @@
         <v>10</v>
       </c>
       <c r="B175" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C175" t="b">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>129</v>
@@ -5689,7 +5670,7 @@
         <v>13</v>
       </c>
       <c r="G175" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
@@ -5697,19 +5678,19 @@
         <v>10</v>
       </c>
       <c r="B176" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D176" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F176" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G176" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
@@ -5717,10 +5698,10 @@
         <v>10</v>
       </c>
       <c r="B177" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D177" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E177" t="s">
         <v>131</v>
@@ -5729,10 +5710,10 @@
         <v>35</v>
       </c>
       <c r="G177" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="K177" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
@@ -5740,19 +5721,19 @@
         <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D178" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E178" t="s">
         <v>132</v>
       </c>
       <c r="F178" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G178" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
@@ -5760,19 +5741,19 @@
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D179" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E179" t="s">
         <v>133</v>
       </c>
       <c r="F179" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G179" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
@@ -5780,10 +5761,10 @@
         <v>10</v>
       </c>
       <c r="B180" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D180" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E180" t="s">
         <v>134</v>
@@ -5800,19 +5781,22 @@
         <v>10</v>
       </c>
       <c r="B181" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D181" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E181" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="F181" t="s">
         <v>25</v>
       </c>
       <c r="H181" t="s">
         <v>25</v>
+      </c>
+      <c r="I181" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.2">
@@ -5820,19 +5804,19 @@
         <v>10</v>
       </c>
       <c r="B182" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D182" t="s">
-        <v>141</v>
-      </c>
-      <c r="E182" t="s">
-        <v>136</v>
+        <v>127</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="F182" t="s">
-        <v>25</v>
-      </c>
-      <c r="H182" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G182" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.2">
@@ -5840,19 +5824,31 @@
         <v>10</v>
       </c>
       <c r="B183" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D183" t="s">
-        <v>141</v>
-      </c>
-      <c r="E183" t="s">
-        <v>137</v>
+        <v>127</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="F183" t="s">
-        <v>25</v>
+        <v>73</v>
+      </c>
+      <c r="G183" t="s">
+        <v>159</v>
       </c>
       <c r="H183" t="s">
-        <v>25</v>
+        <v>170</v>
+      </c>
+      <c r="I183" t="s">
+        <v>171</v>
+      </c>
+      <c r="J183" t="s">
+        <v>17</v>
+      </c>
+      <c r="K183" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.2">
@@ -5860,19 +5856,19 @@
         <v>10</v>
       </c>
       <c r="B184" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D184" t="s">
-        <v>141</v>
-      </c>
-      <c r="E184" t="s">
-        <v>138</v>
+        <v>127</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="F184" t="s">
-        <v>25</v>
-      </c>
-      <c r="H184" t="s">
-        <v>25</v>
+        <v>174</v>
+      </c>
+      <c r="G184" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.2">
@@ -5880,19 +5876,22 @@
         <v>10</v>
       </c>
       <c r="B185" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D185" t="s">
-        <v>141</v>
-      </c>
-      <c r="E185" t="s">
-        <v>139</v>
+        <v>127</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="F185" t="s">
         <v>25</v>
       </c>
       <c r="H185" t="s">
         <v>25</v>
+      </c>
+      <c r="I185">
+        <v>-999</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
@@ -5900,19 +5899,22 @@
         <v>10</v>
       </c>
       <c r="B186" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D186" t="s">
-        <v>141</v>
-      </c>
-      <c r="E186" t="s">
-        <v>140</v>
+        <v>127</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="F186" t="s">
         <v>25</v>
       </c>
       <c r="H186" t="s">
         <v>25</v>
+      </c>
+      <c r="I186" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.2">
@@ -5925,8 +5927,8 @@
       <c r="D187" t="s">
         <v>127</v>
       </c>
-      <c r="E187" t="s">
-        <v>216</v>
+      <c r="E187" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="F187" t="s">
         <v>25</v>
@@ -5935,93 +5937,90 @@
         <v>25</v>
       </c>
       <c r="I187" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>10</v>
       </c>
-      <c r="B188" t="s">
-        <v>127</v>
+      <c r="B188" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="D188" t="s">
-        <v>127</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
+      </c>
+      <c r="E188" t="s">
+        <v>210</v>
       </c>
       <c r="F188" t="s">
-        <v>13</v>
-      </c>
-      <c r="G188" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="H188" t="s">
+        <v>25</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>10</v>
       </c>
-      <c r="B189" t="s">
-        <v>127</v>
+      <c r="B189" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="D189" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="F189" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="G189" t="s">
-        <v>165</v>
-      </c>
-      <c r="H189" t="s">
-        <v>176</v>
-      </c>
-      <c r="I189" t="s">
-        <v>177</v>
-      </c>
-      <c r="J189" t="s">
-        <v>17</v>
-      </c>
-      <c r="K189" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>10</v>
       </c>
-      <c r="B190" t="s">
-        <v>127</v>
+      <c r="B190" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="D190" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F190" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="G190" t="s">
-        <v>181</v>
+        <v>14</v>
+      </c>
+      <c r="H190" t="s">
+        <v>72</v>
+      </c>
+      <c r="I190" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>10</v>
       </c>
-      <c r="B191" t="s">
-        <v>127</v>
+      <c r="B191" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="D191" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="F191" t="s">
         <v>25</v>
@@ -6029,45 +6028,51 @@
       <c r="H191" t="s">
         <v>25</v>
       </c>
-      <c r="I191">
-        <v>-999</v>
+      <c r="I191" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>10</v>
       </c>
-      <c r="B192" t="s">
-        <v>127</v>
+      <c r="B192" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C192" t="b">
+        <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="F192" t="s">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="G192" t="s">
+        <v>212</v>
       </c>
       <c r="H192" t="s">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="I192" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>10</v>
       </c>
-      <c r="B193" t="s">
-        <v>127</v>
+      <c r="B193" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="D193" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="F193" t="s">
         <v>25</v>
@@ -6075,8 +6080,8 @@
       <c r="H193" t="s">
         <v>25</v>
       </c>
-      <c r="I193" t="s">
-        <v>17</v>
+      <c r="I193">
+        <v>-999</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.2">
@@ -6089,8 +6094,8 @@
       <c r="D194" t="s">
         <v>114</v>
       </c>
-      <c r="E194" t="s">
-        <v>216</v>
+      <c r="E194" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F194" t="s">
         <v>25</v>
@@ -6098,8 +6103,11 @@
       <c r="H194" t="s">
         <v>25</v>
       </c>
-      <c r="I194" s="2" t="s">
-        <v>114</v>
+      <c r="I194">
+        <v>-999</v>
+      </c>
+      <c r="J194" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.2">
@@ -6113,13 +6121,13 @@
         <v>114</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="F195" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G195" t="s">
-        <v>14</v>
+        <v>178</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.2">
@@ -6132,20 +6140,14 @@
       <c r="D196" t="s">
         <v>114</v>
       </c>
-      <c r="E196" s="2" t="s">
-        <v>104</v>
+      <c r="E196" t="s">
+        <v>107</v>
       </c>
       <c r="F196" t="s">
-        <v>13</v>
-      </c>
-      <c r="G196" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H196" t="s">
-        <v>72</v>
-      </c>
-      <c r="I196" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.2">
@@ -6158,17 +6160,14 @@
       <c r="D197" t="s">
         <v>114</v>
       </c>
-      <c r="E197" s="2" t="s">
-        <v>92</v>
+      <c r="E197" t="s">
+        <v>108</v>
       </c>
       <c r="F197" t="s">
         <v>25</v>
       </c>
       <c r="H197" t="s">
         <v>25</v>
-      </c>
-      <c r="I197" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.2">
@@ -6178,26 +6177,20 @@
       <c r="B198" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C198" t="b">
-        <v>1</v>
-      </c>
       <c r="D198" t="s">
         <v>114</v>
       </c>
-      <c r="E198" s="2" t="s">
-        <v>105</v>
+      <c r="E198" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="F198" t="s">
-        <v>35</v>
-      </c>
-      <c r="G198" t="s">
-        <v>218</v>
+        <v>25</v>
       </c>
       <c r="H198" t="s">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="I198" t="s">
-        <v>191</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.2">
@@ -6210,17 +6203,14 @@
       <c r="D199" t="s">
         <v>114</v>
       </c>
-      <c r="E199" s="2" t="s">
-        <v>93</v>
+      <c r="E199" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="F199" t="s">
         <v>25</v>
       </c>
       <c r="H199" t="s">
         <v>25</v>
-      </c>
-      <c r="I199">
-        <v>-999</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.2">
@@ -6233,8 +6223,8 @@
       <c r="D200" t="s">
         <v>114</v>
       </c>
-      <c r="E200" s="2" t="s">
-        <v>94</v>
+      <c r="E200" t="s">
+        <v>110</v>
       </c>
       <c r="F200" t="s">
         <v>25</v>
@@ -6242,11 +6232,8 @@
       <c r="H200" t="s">
         <v>25</v>
       </c>
-      <c r="I200">
-        <v>-999</v>
-      </c>
-      <c r="J200" t="s">
-        <v>17</v>
+      <c r="I200" s="4" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.2">
@@ -6259,14 +6246,14 @@
       <c r="D201" t="s">
         <v>114</v>
       </c>
-      <c r="E201" s="2" t="s">
-        <v>106</v>
+      <c r="E201" t="s">
+        <v>111</v>
       </c>
       <c r="F201" t="s">
-        <v>35</v>
-      </c>
-      <c r="G201" t="s">
-        <v>184</v>
+        <v>25</v>
+      </c>
+      <c r="H201" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.2">
@@ -6280,7 +6267,7 @@
         <v>114</v>
       </c>
       <c r="E202" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F202" t="s">
         <v>25</v>
@@ -6300,7 +6287,7 @@
         <v>114</v>
       </c>
       <c r="E203" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F203" t="s">
         <v>25</v>
@@ -6313,14 +6300,14 @@
       <c r="A204" t="s">
         <v>10</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>114</v>
+      <c r="B204" t="s">
+        <v>115</v>
       </c>
       <c r="D204" t="s">
-        <v>114</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>32</v>
+        <v>115</v>
+      </c>
+      <c r="E204" t="s">
+        <v>210</v>
       </c>
       <c r="F204" t="s">
         <v>25</v>
@@ -6329,110 +6316,122 @@
         <v>25</v>
       </c>
       <c r="I204" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>10</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>114</v>
+      <c r="B205" t="s">
+        <v>115</v>
       </c>
       <c r="D205" t="s">
-        <v>114</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>32</v>
+        <v>115</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="F205" t="s">
-        <v>25</v>
-      </c>
-      <c r="H205" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G205" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>10</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>114</v>
+      <c r="B206" t="s">
+        <v>115</v>
       </c>
       <c r="D206" t="s">
-        <v>114</v>
-      </c>
-      <c r="E206" t="s">
-        <v>110</v>
+        <v>115</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F206" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G206" t="s">
+        <v>14</v>
       </c>
       <c r="H206" t="s">
-        <v>25</v>
-      </c>
-      <c r="I206" s="4" t="s">
-        <v>185</v>
+        <v>72</v>
+      </c>
+      <c r="I206" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>10</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>114</v>
+      <c r="B207" t="s">
+        <v>115</v>
       </c>
       <c r="D207" t="s">
-        <v>114</v>
-      </c>
-      <c r="E207" t="s">
-        <v>111</v>
+        <v>115</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="F207" t="s">
         <v>25</v>
       </c>
       <c r="H207" t="s">
         <v>25</v>
+      </c>
+      <c r="I207" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>10</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>114</v>
+      <c r="B208" t="s">
+        <v>115</v>
+      </c>
+      <c r="C208" t="b">
+        <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>114</v>
-      </c>
-      <c r="E208" t="s">
-        <v>112</v>
-      </c>
-      <c r="F208" t="s">
-        <v>25</v>
-      </c>
-      <c r="H208" t="s">
-        <v>25</v>
+        <v>115</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>10</v>
       </c>
-      <c r="B209" s="2" t="s">
-        <v>114</v>
+      <c r="B209" t="s">
+        <v>115</v>
       </c>
       <c r="D209" t="s">
-        <v>114</v>
-      </c>
-      <c r="E209" t="s">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F209" t="s">
         <v>25</v>
       </c>
       <c r="H209" t="s">
         <v>25</v>
+      </c>
+      <c r="I209">
+        <v>-999</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.2">
@@ -6445,8 +6444,8 @@
       <c r="D210" t="s">
         <v>115</v>
       </c>
-      <c r="E210" t="s">
-        <v>216</v>
+      <c r="E210" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F210" t="s">
         <v>25</v>
@@ -6454,8 +6453,8 @@
       <c r="H210" t="s">
         <v>25</v>
       </c>
-      <c r="I210" t="s">
-        <v>115</v>
+      <c r="I210">
+        <v>-999</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.2">
@@ -6463,19 +6462,22 @@
         <v>10</v>
       </c>
       <c r="B211" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D211" t="s">
-        <v>115</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>71</v>
+        <v>121</v>
+      </c>
+      <c r="E211" t="s">
+        <v>210</v>
       </c>
       <c r="F211" t="s">
-        <v>13</v>
-      </c>
-      <c r="G211" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="H211" t="s">
+        <v>25</v>
+      </c>
+      <c r="I211" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.2">
@@ -6483,13 +6485,13 @@
         <v>10</v>
       </c>
       <c r="B212" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D212" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="F212" t="s">
         <v>13</v>
@@ -6497,34 +6499,31 @@
       <c r="G212" t="s">
         <v>14</v>
       </c>
-      <c r="H212" t="s">
-        <v>72</v>
-      </c>
-      <c r="I212" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>10</v>
       </c>
       <c r="B213" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D213" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="F213" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G213" t="s">
+        <v>14</v>
       </c>
       <c r="H213" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="I213" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.2">
@@ -6532,22 +6531,25 @@
         <v>10</v>
       </c>
       <c r="B214" t="s">
-        <v>115</v>
-      </c>
-      <c r="C214" t="b">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="D214" t="s">
-        <v>115</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G214" s="2" t="s">
-        <v>186</v>
+        <v>121</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F214" t="s">
+        <v>25</v>
+      </c>
+      <c r="H214" t="s">
+        <v>25</v>
+      </c>
+      <c r="I214" t="s">
+        <v>181</v>
+      </c>
+      <c r="J214" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.2">
@@ -6555,22 +6557,25 @@
         <v>10</v>
       </c>
       <c r="B215" t="s">
-        <v>115</v>
+        <v>121</v>
+      </c>
+      <c r="C215" t="b">
+        <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>115</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="F215" t="s">
-        <v>25</v>
-      </c>
-      <c r="H215" t="s">
-        <v>25</v>
-      </c>
-      <c r="I215">
-        <v>-999</v>
+        <v>119</v>
+      </c>
+      <c r="G215" t="s">
+        <v>211</v>
+      </c>
+      <c r="J215" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.2">
@@ -6578,21 +6583,21 @@
         <v>10</v>
       </c>
       <c r="B216" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D216" t="s">
-        <v>115</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>94</v>
+        <v>121</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="F216" t="s">
-        <v>25</v>
-      </c>
-      <c r="H216" t="s">
-        <v>25</v>
-      </c>
-      <c r="I216">
+        <v>154</v>
+      </c>
+      <c r="G216" t="s">
+        <v>182</v>
+      </c>
+      <c r="J216">
         <v>-999</v>
       </c>
     </row>
@@ -6606,17 +6611,17 @@
       <c r="D217" t="s">
         <v>121</v>
       </c>
-      <c r="E217" t="s">
-        <v>216</v>
+      <c r="E217" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="F217" t="s">
-        <v>25</v>
-      </c>
-      <c r="H217" t="s">
-        <v>25</v>
-      </c>
-      <c r="I217" t="s">
-        <v>121</v>
+        <v>154</v>
+      </c>
+      <c r="G217" t="s">
+        <v>182</v>
+      </c>
+      <c r="J217">
+        <v>-999</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.2">
@@ -6629,14 +6634,17 @@
       <c r="D218" t="s">
         <v>121</v>
       </c>
-      <c r="E218" s="2" t="s">
-        <v>71</v>
+      <c r="E218" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="F218" t="s">
-        <v>13</v>
-      </c>
-      <c r="G218" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="H218" t="s">
+        <v>25</v>
+      </c>
+      <c r="I218" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.2">
@@ -6649,20 +6657,17 @@
       <c r="D219" t="s">
         <v>121</v>
       </c>
-      <c r="E219" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F219" t="s">
-        <v>13</v>
+      <c r="E219" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="G219" t="s">
-        <v>14</v>
-      </c>
-      <c r="H219" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="I219" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.2">
@@ -6670,13 +6675,13 @@
         <v>10</v>
       </c>
       <c r="B220" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D220" t="s">
-        <v>121</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="E220" t="s">
+        <v>210</v>
       </c>
       <c r="F220" t="s">
         <v>25</v>
@@ -6685,10 +6690,7 @@
         <v>25</v>
       </c>
       <c r="I220" t="s">
-        <v>187</v>
-      </c>
-      <c r="J220" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.2">
@@ -6696,25 +6698,19 @@
         <v>10</v>
       </c>
       <c r="B221" t="s">
-        <v>121</v>
-      </c>
-      <c r="C221" t="b">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="D221" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="F221" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G221" t="s">
-        <v>217</v>
-      </c>
-      <c r="J221" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.2">
@@ -6722,22 +6718,25 @@
         <v>10</v>
       </c>
       <c r="B222" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D222" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F222" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="G222" t="s">
-        <v>188</v>
-      </c>
-      <c r="J222">
-        <v>-999</v>
+        <v>14</v>
+      </c>
+      <c r="H222" t="s">
+        <v>72</v>
+      </c>
+      <c r="I222" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.2">
@@ -6745,22 +6744,22 @@
         <v>10</v>
       </c>
       <c r="B223" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D223" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F223" t="s">
-        <v>160</v>
-      </c>
-      <c r="G223" t="s">
-        <v>188</v>
-      </c>
-      <c r="J223">
-        <v>-999</v>
+        <v>25</v>
+      </c>
+      <c r="H223" t="s">
+        <v>25</v>
+      </c>
+      <c r="I223" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.2">
@@ -6768,13 +6767,13 @@
         <v>10</v>
       </c>
       <c r="B224" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D224" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="F224" t="s">
         <v>25</v>
@@ -6783,7 +6782,7 @@
         <v>25</v>
       </c>
       <c r="I224" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
@@ -6791,22 +6790,22 @@
         <v>10</v>
       </c>
       <c r="B225" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D225" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G225" t="s">
-        <v>213</v>
-      </c>
-      <c r="I225" t="s">
-        <v>189</v>
+        <v>93</v>
+      </c>
+      <c r="F225" t="s">
+        <v>25</v>
+      </c>
+      <c r="H225" t="s">
+        <v>25</v>
+      </c>
+      <c r="I225">
+        <v>-999</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
@@ -6814,13 +6813,13 @@
         <v>10</v>
       </c>
       <c r="B226" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D226" t="s">
         <v>103</v>
       </c>
-      <c r="E226" t="s">
-        <v>216</v>
+      <c r="E226" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="F226" t="s">
         <v>25</v>
@@ -6828,8 +6827,8 @@
       <c r="H226" t="s">
         <v>25</v>
       </c>
-      <c r="I226" t="s">
-        <v>103</v>
+      <c r="I226">
+        <v>-999</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
@@ -6837,19 +6836,22 @@
         <v>10</v>
       </c>
       <c r="B227" t="s">
-        <v>192</v>
+        <v>186</v>
+      </c>
+      <c r="C227" t="b">
+        <v>1</v>
       </c>
       <c r="D227" t="s">
         <v>103</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F227" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G227" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
@@ -6857,25 +6859,19 @@
         <v>10</v>
       </c>
       <c r="B228" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D228" t="s">
         <v>103</v>
       </c>
-      <c r="E228" s="3" t="s">
-        <v>91</v>
+      <c r="E228" t="s">
+        <v>96</v>
       </c>
       <c r="F228" t="s">
-        <v>13</v>
-      </c>
-      <c r="G228" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H228" t="s">
-        <v>72</v>
-      </c>
-      <c r="I228" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
@@ -6883,22 +6879,19 @@
         <v>10</v>
       </c>
       <c r="B229" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D229" t="s">
         <v>103</v>
       </c>
-      <c r="E229" s="3" t="s">
-        <v>92</v>
+      <c r="E229" t="s">
+        <v>97</v>
       </c>
       <c r="F229" t="s">
         <v>25</v>
       </c>
       <c r="H229" t="s">
         <v>25</v>
-      </c>
-      <c r="I229" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
@@ -6906,22 +6899,19 @@
         <v>10</v>
       </c>
       <c r="B230" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D230" t="s">
         <v>103</v>
       </c>
-      <c r="E230" s="3" t="s">
-        <v>212</v>
+      <c r="E230" t="s">
+        <v>98</v>
       </c>
       <c r="F230" t="s">
         <v>25</v>
       </c>
       <c r="H230" t="s">
         <v>25</v>
-      </c>
-      <c r="I230" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
@@ -6929,22 +6919,19 @@
         <v>10</v>
       </c>
       <c r="B231" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D231" t="s">
         <v>103</v>
       </c>
-      <c r="E231" s="3" t="s">
-        <v>93</v>
+      <c r="E231" t="s">
+        <v>99</v>
       </c>
       <c r="F231" t="s">
         <v>25</v>
       </c>
       <c r="H231" t="s">
         <v>25</v>
-      </c>
-      <c r="I231">
-        <v>-999</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
@@ -6952,22 +6939,19 @@
         <v>10</v>
       </c>
       <c r="B232" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D232" t="s">
         <v>103</v>
       </c>
-      <c r="E232" s="3" t="s">
-        <v>94</v>
+      <c r="E232" t="s">
+        <v>100</v>
       </c>
       <c r="F232" t="s">
         <v>25</v>
       </c>
       <c r="H232" t="s">
         <v>25</v>
-      </c>
-      <c r="I232">
-        <v>-999</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
@@ -6975,22 +6959,19 @@
         <v>10</v>
       </c>
       <c r="B233" t="s">
-        <v>192</v>
-      </c>
-      <c r="C233" t="b">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="D233" t="s">
         <v>103</v>
       </c>
-      <c r="E233" s="3" t="s">
-        <v>95</v>
+      <c r="E233" t="s">
+        <v>101</v>
       </c>
       <c r="F233" t="s">
-        <v>35</v>
-      </c>
-      <c r="G233" t="s">
-        <v>194</v>
+        <v>25</v>
+      </c>
+      <c r="H233" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
@@ -6998,13 +6979,13 @@
         <v>10</v>
       </c>
       <c r="B234" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D234" t="s">
         <v>103</v>
       </c>
       <c r="E234" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F234" t="s">
         <v>25</v>
@@ -7018,19 +6999,22 @@
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D235" t="s">
         <v>103</v>
       </c>
       <c r="E235" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="F235" t="s">
         <v>25</v>
       </c>
       <c r="H235" t="s">
         <v>25</v>
+      </c>
+      <c r="I235" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
@@ -7038,19 +7022,19 @@
         <v>10</v>
       </c>
       <c r="B236" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D236" t="s">
         <v>103</v>
       </c>
-      <c r="E236" t="s">
-        <v>98</v>
+      <c r="E236" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="F236" t="s">
-        <v>25</v>
-      </c>
-      <c r="H236" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G236" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
@@ -7058,19 +7042,25 @@
         <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D237" t="s">
         <v>103</v>
       </c>
-      <c r="E237" t="s">
-        <v>99</v>
+      <c r="E237" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="F237" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G237" t="s">
+        <v>14</v>
       </c>
       <c r="H237" t="s">
-        <v>25</v>
+        <v>72</v>
+      </c>
+      <c r="I237" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
@@ -7078,19 +7068,22 @@
         <v>10</v>
       </c>
       <c r="B238" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D238" t="s">
         <v>103</v>
       </c>
-      <c r="E238" t="s">
-        <v>100</v>
+      <c r="E238" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="F238" t="s">
         <v>25</v>
       </c>
       <c r="H238" t="s">
         <v>25</v>
+      </c>
+      <c r="I238" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
@@ -7098,19 +7091,22 @@
         <v>10</v>
       </c>
       <c r="B239" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D239" t="s">
         <v>103</v>
       </c>
-      <c r="E239" t="s">
-        <v>101</v>
+      <c r="E239" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="F239" t="s">
         <v>25</v>
       </c>
       <c r="H239" t="s">
         <v>25</v>
+      </c>
+      <c r="I239" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
@@ -7118,19 +7114,22 @@
         <v>10</v>
       </c>
       <c r="B240" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D240" t="s">
         <v>103</v>
       </c>
-      <c r="E240" t="s">
-        <v>102</v>
+      <c r="E240" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F240" t="s">
         <v>25</v>
       </c>
       <c r="H240" t="s">
         <v>25</v>
+      </c>
+      <c r="I240">
+        <v>-999</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
@@ -7138,13 +7137,13 @@
         <v>10</v>
       </c>
       <c r="B241" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D241" t="s">
         <v>103</v>
       </c>
-      <c r="E241" t="s">
-        <v>216</v>
+      <c r="E241" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F241" t="s">
         <v>25</v>
@@ -7152,8 +7151,8 @@
       <c r="H241" t="s">
         <v>25</v>
       </c>
-      <c r="I241" t="s">
-        <v>103</v>
+      <c r="I241">
+        <v>-999</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -7161,19 +7160,22 @@
         <v>10</v>
       </c>
       <c r="B242" t="s">
-        <v>196</v>
+        <v>190</v>
+      </c>
+      <c r="C242" t="b">
+        <v>1</v>
       </c>
       <c r="D242" t="s">
         <v>103</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F242" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G242" t="s">
-        <v>14</v>
+        <v>193</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
@@ -7181,25 +7183,19 @@
         <v>10</v>
       </c>
       <c r="B243" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D243" t="s">
         <v>103</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>91</v>
+      <c r="E243" t="s">
+        <v>96</v>
       </c>
       <c r="F243" t="s">
-        <v>13</v>
-      </c>
-      <c r="G243" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H243" t="s">
-        <v>72</v>
-      </c>
-      <c r="I243" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
@@ -7207,22 +7203,19 @@
         <v>10</v>
       </c>
       <c r="B244" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D244" t="s">
         <v>103</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>92</v>
+      <c r="E244" t="s">
+        <v>97</v>
       </c>
       <c r="F244" t="s">
         <v>25</v>
       </c>
       <c r="H244" t="s">
         <v>25</v>
-      </c>
-      <c r="I244" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
@@ -7230,22 +7223,19 @@
         <v>10</v>
       </c>
       <c r="B245" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D245" t="s">
         <v>103</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>212</v>
+      <c r="E245" t="s">
+        <v>98</v>
       </c>
       <c r="F245" t="s">
         <v>25</v>
       </c>
       <c r="H245" t="s">
         <v>25</v>
-      </c>
-      <c r="I245" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -7253,22 +7243,19 @@
         <v>10</v>
       </c>
       <c r="B246" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D246" t="s">
         <v>103</v>
       </c>
-      <c r="E246" s="2" t="s">
-        <v>93</v>
+      <c r="E246" t="s">
+        <v>99</v>
       </c>
       <c r="F246" t="s">
         <v>25</v>
       </c>
       <c r="H246" t="s">
         <v>25</v>
-      </c>
-      <c r="I246">
-        <v>-999</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
@@ -7276,22 +7263,19 @@
         <v>10</v>
       </c>
       <c r="B247" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D247" t="s">
         <v>103</v>
       </c>
-      <c r="E247" s="2" t="s">
-        <v>94</v>
+      <c r="E247" t="s">
+        <v>100</v>
       </c>
       <c r="F247" t="s">
         <v>25</v>
       </c>
       <c r="H247" t="s">
         <v>25</v>
-      </c>
-      <c r="I247">
-        <v>-999</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
@@ -7299,22 +7283,19 @@
         <v>10</v>
       </c>
       <c r="B248" t="s">
-        <v>196</v>
-      </c>
-      <c r="C248" t="b">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="D248" t="s">
         <v>103</v>
       </c>
-      <c r="E248" s="2" t="s">
-        <v>95</v>
+      <c r="E248" t="s">
+        <v>101</v>
       </c>
       <c r="F248" t="s">
-        <v>35</v>
-      </c>
-      <c r="G248" t="s">
-        <v>199</v>
+        <v>25</v>
+      </c>
+      <c r="H248" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
@@ -7322,13 +7303,13 @@
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D249" t="s">
         <v>103</v>
       </c>
       <c r="E249" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F249" t="s">
         <v>25</v>
@@ -7342,19 +7323,22 @@
         <v>10</v>
       </c>
       <c r="B250" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D250" t="s">
         <v>103</v>
       </c>
       <c r="E250" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="F250" t="s">
         <v>25</v>
       </c>
       <c r="H250" t="s">
         <v>25</v>
+      </c>
+      <c r="I250" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
@@ -7362,19 +7346,19 @@
         <v>10</v>
       </c>
       <c r="B251" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D251" t="s">
         <v>103</v>
       </c>
-      <c r="E251" t="s">
-        <v>98</v>
+      <c r="E251" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="F251" t="s">
-        <v>25</v>
-      </c>
-      <c r="H251" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G251" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
@@ -7382,19 +7366,25 @@
         <v>10</v>
       </c>
       <c r="B252" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D252" t="s">
         <v>103</v>
       </c>
-      <c r="E252" t="s">
-        <v>99</v>
+      <c r="E252" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="F252" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G252" t="s">
+        <v>14</v>
       </c>
       <c r="H252" t="s">
-        <v>25</v>
+        <v>72</v>
+      </c>
+      <c r="I252" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
@@ -7402,19 +7392,22 @@
         <v>10</v>
       </c>
       <c r="B253" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D253" t="s">
         <v>103</v>
       </c>
-      <c r="E253" t="s">
-        <v>100</v>
+      <c r="E253" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="F253" t="s">
         <v>25</v>
       </c>
       <c r="H253" t="s">
         <v>25</v>
+      </c>
+      <c r="I253" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
@@ -7422,19 +7415,22 @@
         <v>10</v>
       </c>
       <c r="B254" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D254" t="s">
         <v>103</v>
       </c>
-      <c r="E254" t="s">
-        <v>101</v>
+      <c r="E254" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="F254" t="s">
         <v>25</v>
       </c>
       <c r="H254" t="s">
         <v>25</v>
+      </c>
+      <c r="I254" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
@@ -7442,19 +7438,22 @@
         <v>10</v>
       </c>
       <c r="B255" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D255" t="s">
         <v>103</v>
       </c>
-      <c r="E255" t="s">
-        <v>102</v>
+      <c r="E255" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F255" t="s">
         <v>25</v>
       </c>
       <c r="H255" t="s">
         <v>25</v>
+      </c>
+      <c r="I255">
+        <v>-999</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
@@ -7462,13 +7461,13 @@
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D256" t="s">
         <v>103</v>
       </c>
-      <c r="E256" t="s">
-        <v>216</v>
+      <c r="E256" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F256" t="s">
         <v>25</v>
@@ -7476,8 +7475,8 @@
       <c r="H256" t="s">
         <v>25</v>
       </c>
-      <c r="I256" t="s">
-        <v>103</v>
+      <c r="I256">
+        <v>-999</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
@@ -7485,19 +7484,22 @@
         <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>201</v>
+        <v>195</v>
+      </c>
+      <c r="C257" t="b">
+        <v>1</v>
       </c>
       <c r="D257" t="s">
         <v>103</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F257" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G257" t="s">
-        <v>14</v>
+        <v>196</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
@@ -7505,25 +7507,19 @@
         <v>10</v>
       </c>
       <c r="B258" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D258" t="s">
         <v>103</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>91</v>
+      <c r="E258" t="s">
+        <v>96</v>
       </c>
       <c r="F258" t="s">
-        <v>13</v>
-      </c>
-      <c r="G258" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H258" t="s">
-        <v>72</v>
-      </c>
-      <c r="I258" t="s">
-        <v>200</v>
+        <v>25</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
@@ -7531,22 +7527,19 @@
         <v>10</v>
       </c>
       <c r="B259" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D259" t="s">
         <v>103</v>
       </c>
-      <c r="E259" s="2" t="s">
-        <v>92</v>
+      <c r="E259" t="s">
+        <v>97</v>
       </c>
       <c r="F259" t="s">
         <v>25</v>
       </c>
       <c r="H259" t="s">
         <v>25</v>
-      </c>
-      <c r="I259" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
@@ -7554,22 +7547,19 @@
         <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D260" t="s">
         <v>103</v>
       </c>
-      <c r="E260" s="2" t="s">
-        <v>212</v>
+      <c r="E260" t="s">
+        <v>98</v>
       </c>
       <c r="F260" t="s">
         <v>25</v>
       </c>
       <c r="H260" t="s">
         <v>25</v>
-      </c>
-      <c r="I260" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
@@ -7577,22 +7567,19 @@
         <v>10</v>
       </c>
       <c r="B261" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D261" t="s">
         <v>103</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>93</v>
+      <c r="E261" t="s">
+        <v>99</v>
       </c>
       <c r="F261" t="s">
         <v>25</v>
       </c>
       <c r="H261" t="s">
         <v>25</v>
-      </c>
-      <c r="I261">
-        <v>-999</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
@@ -7600,22 +7587,19 @@
         <v>10</v>
       </c>
       <c r="B262" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D262" t="s">
         <v>103</v>
       </c>
-      <c r="E262" s="2" t="s">
-        <v>94</v>
+      <c r="E262" t="s">
+        <v>100</v>
       </c>
       <c r="F262" t="s">
         <v>25</v>
       </c>
       <c r="H262" t="s">
         <v>25</v>
-      </c>
-      <c r="I262">
-        <v>-999</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
@@ -7623,22 +7607,19 @@
         <v>10</v>
       </c>
       <c r="B263" t="s">
-        <v>201</v>
-      </c>
-      <c r="C263" t="b">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="D263" t="s">
         <v>103</v>
       </c>
-      <c r="E263" s="2" t="s">
-        <v>95</v>
+      <c r="E263" t="s">
+        <v>101</v>
       </c>
       <c r="F263" t="s">
-        <v>35</v>
-      </c>
-      <c r="G263" t="s">
-        <v>202</v>
+        <v>25</v>
+      </c>
+      <c r="H263" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
@@ -7646,13 +7627,13 @@
         <v>10</v>
       </c>
       <c r="B264" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D264" t="s">
         <v>103</v>
       </c>
       <c r="E264" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F264" t="s">
         <v>25</v>
@@ -7666,19 +7647,22 @@
         <v>10</v>
       </c>
       <c r="B265" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D265" t="s">
         <v>103</v>
       </c>
       <c r="E265" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="F265" t="s">
         <v>25</v>
       </c>
       <c r="H265" t="s">
         <v>25</v>
+      </c>
+      <c r="I265" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
@@ -7686,19 +7670,19 @@
         <v>10</v>
       </c>
       <c r="B266" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D266" t="s">
         <v>103</v>
       </c>
-      <c r="E266" t="s">
-        <v>98</v>
+      <c r="E266" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="F266" t="s">
-        <v>25</v>
-      </c>
-      <c r="H266" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G266" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
@@ -7706,19 +7690,25 @@
         <v>10</v>
       </c>
       <c r="B267" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D267" t="s">
         <v>103</v>
       </c>
-      <c r="E267" t="s">
-        <v>99</v>
+      <c r="E267" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="F267" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G267" t="s">
+        <v>14</v>
       </c>
       <c r="H267" t="s">
-        <v>25</v>
+        <v>72</v>
+      </c>
+      <c r="I267" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
@@ -7726,19 +7716,22 @@
         <v>10</v>
       </c>
       <c r="B268" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D268" t="s">
         <v>103</v>
       </c>
-      <c r="E268" t="s">
-        <v>100</v>
+      <c r="E268" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="F268" t="s">
         <v>25</v>
       </c>
       <c r="H268" t="s">
         <v>25</v>
+      </c>
+      <c r="I268" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
@@ -7746,19 +7739,22 @@
         <v>10</v>
       </c>
       <c r="B269" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D269" t="s">
         <v>103</v>
       </c>
-      <c r="E269" t="s">
-        <v>101</v>
+      <c r="E269" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="F269" t="s">
         <v>25</v>
       </c>
       <c r="H269" t="s">
         <v>25</v>
+      </c>
+      <c r="I269" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
@@ -7766,19 +7762,22 @@
         <v>10</v>
       </c>
       <c r="B270" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D270" t="s">
         <v>103</v>
       </c>
-      <c r="E270" t="s">
-        <v>102</v>
+      <c r="E270" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F270" t="s">
         <v>25</v>
       </c>
       <c r="H270" t="s">
         <v>25</v>
+      </c>
+      <c r="I270">
+        <v>-999</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
@@ -7786,13 +7785,13 @@
         <v>10</v>
       </c>
       <c r="B271" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D271" t="s">
         <v>103</v>
       </c>
-      <c r="E271" t="s">
-        <v>216</v>
+      <c r="E271" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F271" t="s">
         <v>25</v>
@@ -7800,8 +7799,8 @@
       <c r="H271" t="s">
         <v>25</v>
       </c>
-      <c r="I271" t="s">
-        <v>103</v>
+      <c r="I271">
+        <v>-999</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
@@ -7809,19 +7808,22 @@
         <v>10</v>
       </c>
       <c r="B272" t="s">
-        <v>203</v>
+        <v>197</v>
+      </c>
+      <c r="C272" t="b">
+        <v>1</v>
       </c>
       <c r="D272" t="s">
         <v>103</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F272" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G272" t="s">
-        <v>14</v>
+        <v>200</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.2">
@@ -7829,25 +7831,19 @@
         <v>10</v>
       </c>
       <c r="B273" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D273" t="s">
         <v>103</v>
       </c>
-      <c r="E273" s="2" t="s">
-        <v>91</v>
+      <c r="E273" t="s">
+        <v>96</v>
       </c>
       <c r="F273" t="s">
-        <v>13</v>
-      </c>
-      <c r="G273" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H273" t="s">
-        <v>72</v>
-      </c>
-      <c r="I273" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
@@ -7855,22 +7851,19 @@
         <v>10</v>
       </c>
       <c r="B274" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D274" t="s">
         <v>103</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>92</v>
+      <c r="E274" t="s">
+        <v>97</v>
       </c>
       <c r="F274" t="s">
         <v>25</v>
       </c>
       <c r="H274" t="s">
         <v>25</v>
-      </c>
-      <c r="I274" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
@@ -7878,22 +7871,19 @@
         <v>10</v>
       </c>
       <c r="B275" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D275" t="s">
         <v>103</v>
       </c>
-      <c r="E275" s="2" t="s">
-        <v>212</v>
+      <c r="E275" t="s">
+        <v>98</v>
       </c>
       <c r="F275" t="s">
         <v>25</v>
       </c>
       <c r="H275" t="s">
         <v>25</v>
-      </c>
-      <c r="I275" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
@@ -7901,22 +7891,19 @@
         <v>10</v>
       </c>
       <c r="B276" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D276" t="s">
         <v>103</v>
       </c>
-      <c r="E276" s="2" t="s">
-        <v>93</v>
+      <c r="E276" t="s">
+        <v>99</v>
       </c>
       <c r="F276" t="s">
         <v>25</v>
       </c>
       <c r="H276" t="s">
         <v>25</v>
-      </c>
-      <c r="I276">
-        <v>-999</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.2">
@@ -7924,22 +7911,19 @@
         <v>10</v>
       </c>
       <c r="B277" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D277" t="s">
         <v>103</v>
       </c>
-      <c r="E277" s="2" t="s">
-        <v>94</v>
+      <c r="E277" t="s">
+        <v>100</v>
       </c>
       <c r="F277" t="s">
         <v>25</v>
       </c>
       <c r="H277" t="s">
         <v>25</v>
-      </c>
-      <c r="I277">
-        <v>-999</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.2">
@@ -7947,22 +7931,19 @@
         <v>10</v>
       </c>
       <c r="B278" t="s">
-        <v>203</v>
-      </c>
-      <c r="C278" t="b">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="D278" t="s">
         <v>103</v>
       </c>
-      <c r="E278" s="2" t="s">
-        <v>95</v>
+      <c r="E278" t="s">
+        <v>101</v>
       </c>
       <c r="F278" t="s">
-        <v>35</v>
-      </c>
-      <c r="G278" t="s">
-        <v>206</v>
+        <v>25</v>
+      </c>
+      <c r="H278" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
@@ -7970,13 +7951,13 @@
         <v>10</v>
       </c>
       <c r="B279" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D279" t="s">
         <v>103</v>
       </c>
       <c r="E279" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F279" t="s">
         <v>25</v>
@@ -7990,19 +7971,22 @@
         <v>10</v>
       </c>
       <c r="B280" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D280" t="s">
         <v>103</v>
       </c>
       <c r="E280" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="F280" t="s">
         <v>25</v>
       </c>
       <c r="H280" t="s">
         <v>25</v>
+      </c>
+      <c r="I280" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.2">
@@ -8010,19 +7994,19 @@
         <v>10</v>
       </c>
       <c r="B281" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D281" t="s">
         <v>103</v>
       </c>
-      <c r="E281" t="s">
-        <v>98</v>
+      <c r="E281" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="F281" t="s">
-        <v>25</v>
-      </c>
-      <c r="H281" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="G281" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.2">
@@ -8030,39 +8014,44 @@
         <v>10</v>
       </c>
       <c r="B282" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D282" t="s">
         <v>103</v>
       </c>
-      <c r="E282" t="s">
-        <v>99</v>
-      </c>
-      <c r="F282" t="s">
-        <v>25</v>
-      </c>
-      <c r="H282" t="s">
-        <v>25</v>
-      </c>
+      <c r="E282" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H282" s="2"/>
+      <c r="I282" s="2"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>10</v>
       </c>
       <c r="B283" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D283" t="s">
         <v>103</v>
       </c>
-      <c r="E283" t="s">
-        <v>100</v>
-      </c>
-      <c r="F283" t="s">
+      <c r="E283" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H283" t="s">
         <v>25</v>
+      </c>
+      <c r="I283" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.2">
@@ -8070,19 +8059,19 @@
         <v>10</v>
       </c>
       <c r="B284" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D284" t="s">
         <v>103</v>
       </c>
-      <c r="E284" t="s">
-        <v>101</v>
+      <c r="E284" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="F284" t="s">
-        <v>25</v>
-      </c>
-      <c r="H284" t="s">
-        <v>25</v>
+        <v>205</v>
+      </c>
+      <c r="G284" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.2">
@@ -8090,19 +8079,22 @@
         <v>10</v>
       </c>
       <c r="B285" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D285" t="s">
         <v>103</v>
       </c>
-      <c r="E285" t="s">
-        <v>102</v>
+      <c r="E285" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F285" t="s">
         <v>25</v>
       </c>
       <c r="H285" t="s">
         <v>25</v>
+      </c>
+      <c r="I285">
+        <v>-999</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.2">
@@ -8110,13 +8102,13 @@
         <v>10</v>
       </c>
       <c r="B286" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D286" t="s">
         <v>103</v>
       </c>
-      <c r="E286" t="s">
-        <v>216</v>
+      <c r="E286" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F286" t="s">
         <v>25</v>
@@ -8124,8 +8116,8 @@
       <c r="H286" t="s">
         <v>25</v>
       </c>
-      <c r="I286" t="s">
-        <v>103</v>
+      <c r="I286">
+        <v>-999</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
@@ -8133,19 +8125,22 @@
         <v>10</v>
       </c>
       <c r="B287" t="s">
-        <v>207</v>
+        <v>201</v>
+      </c>
+      <c r="C287" t="b">
+        <v>1</v>
       </c>
       <c r="D287" t="s">
         <v>103</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F287" t="s">
+        <v>95</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G287" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.2">
@@ -8153,44 +8148,39 @@
         <v>10</v>
       </c>
       <c r="B288" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D288" t="s">
         <v>103</v>
       </c>
-      <c r="E288" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G288" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H288" s="2"/>
-      <c r="I288" s="2"/>
+      <c r="E288" t="s">
+        <v>96</v>
+      </c>
+      <c r="F288" t="s">
+        <v>25</v>
+      </c>
+      <c r="H288" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>10</v>
       </c>
       <c r="B289" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D289" t="s">
         <v>103</v>
       </c>
-      <c r="E289" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F289" s="2" t="s">
+      <c r="E289" t="s">
+        <v>97</v>
+      </c>
+      <c r="F289" t="s">
         <v>25</v>
       </c>
       <c r="H289" t="s">
         <v>25</v>
-      </c>
-      <c r="I289" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -8198,19 +8188,19 @@
         <v>10</v>
       </c>
       <c r="B290" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D290" t="s">
         <v>103</v>
       </c>
-      <c r="E290" s="2" t="s">
-        <v>212</v>
+      <c r="E290" t="s">
+        <v>98</v>
       </c>
       <c r="F290" t="s">
-        <v>211</v>
-      </c>
-      <c r="G290" t="s">
-        <v>209</v>
+        <v>25</v>
+      </c>
+      <c r="H290" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -8218,22 +8208,19 @@
         <v>10</v>
       </c>
       <c r="B291" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D291" t="s">
         <v>103</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>93</v>
+      <c r="E291" t="s">
+        <v>99</v>
       </c>
       <c r="F291" t="s">
         <v>25</v>
       </c>
       <c r="H291" t="s">
         <v>25</v>
-      </c>
-      <c r="I291">
-        <v>-999</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
@@ -8241,22 +8228,19 @@
         <v>10</v>
       </c>
       <c r="B292" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D292" t="s">
         <v>103</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>94</v>
+      <c r="E292" t="s">
+        <v>100</v>
       </c>
       <c r="F292" t="s">
         <v>25</v>
       </c>
       <c r="H292" t="s">
         <v>25</v>
-      </c>
-      <c r="I292">
-        <v>-999</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
@@ -8264,22 +8248,19 @@
         <v>10</v>
       </c>
       <c r="B293" t="s">
-        <v>207</v>
-      </c>
-      <c r="C293" t="b">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="D293" t="s">
         <v>103</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G293" t="s">
-        <v>209</v>
+      <c r="E293" t="s">
+        <v>101</v>
+      </c>
+      <c r="F293" t="s">
+        <v>25</v>
+      </c>
+      <c r="H293" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
@@ -8287,13 +8268,13 @@
         <v>10</v>
       </c>
       <c r="B294" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D294" t="s">
         <v>103</v>
       </c>
       <c r="E294" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F294" t="s">
         <v>25</v>
@@ -8307,19 +8288,22 @@
         <v>10</v>
       </c>
       <c r="B295" t="s">
-        <v>207</v>
+        <v>49</v>
+      </c>
+      <c r="C295" t="b">
+        <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="E295" t="s">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="F295" t="s">
-        <v>25</v>
-      </c>
-      <c r="H295" t="s">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="G295" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
@@ -8327,19 +8311,19 @@
         <v>10</v>
       </c>
       <c r="B296" t="s">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="D296" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="E296" t="s">
-        <v>98</v>
+        <v>213</v>
       </c>
       <c r="F296" t="s">
-        <v>25</v>
-      </c>
-      <c r="H296" t="s">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="G296" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
@@ -8347,19 +8331,19 @@
         <v>10</v>
       </c>
       <c r="B297" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="D297" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="E297" t="s">
-        <v>99</v>
+        <v>213</v>
       </c>
       <c r="F297" t="s">
-        <v>25</v>
-      </c>
-      <c r="H297" t="s">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="G297" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
@@ -8367,19 +8351,22 @@
         <v>10</v>
       </c>
       <c r="B298" t="s">
-        <v>207</v>
+        <v>78</v>
+      </c>
+      <c r="C298" t="b">
+        <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="E298" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="F298" t="s">
-        <v>25</v>
-      </c>
-      <c r="H298" t="s">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="G298" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
@@ -8387,19 +8374,19 @@
         <v>10</v>
       </c>
       <c r="B299" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="D299" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="E299" t="s">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="F299" t="s">
-        <v>25</v>
-      </c>
-      <c r="H299" t="s">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="G299" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
@@ -8407,19 +8394,19 @@
         <v>10</v>
       </c>
       <c r="B300" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
       <c r="D300" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="E300" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="F300" t="s">
-        <v>25</v>
-      </c>
-      <c r="H300" t="s">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="G300" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
@@ -8427,7 +8414,7 @@
         <v>10</v>
       </c>
       <c r="B301" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C301" t="b">
         <v>1</v>
@@ -8436,13 +8423,13 @@
         <v>20</v>
       </c>
       <c r="E301" t="s">
-        <v>219</v>
-      </c>
-      <c r="F301" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F301" t="s">
         <v>50</v>
       </c>
       <c r="G301" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
@@ -8450,19 +8437,19 @@
         <v>10</v>
       </c>
       <c r="B302" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D302" t="s">
         <v>20</v>
       </c>
       <c r="E302" t="s">
-        <v>219</v>
-      </c>
-      <c r="F302" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F302" t="s">
         <v>50</v>
       </c>
       <c r="G302" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
@@ -8470,19 +8457,19 @@
         <v>10</v>
       </c>
       <c r="B303" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D303" t="s">
         <v>20</v>
       </c>
       <c r="E303" t="s">
-        <v>219</v>
-      </c>
-      <c r="F303" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F303" t="s">
         <v>50</v>
       </c>
       <c r="G303" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
@@ -8490,22 +8477,22 @@
         <v>10</v>
       </c>
       <c r="B304" t="s">
-        <v>78</v>
-      </c>
-      <c r="C304" t="b">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="D304" t="s">
         <v>20</v>
       </c>
       <c r="E304" t="s">
-        <v>219</v>
-      </c>
-      <c r="F304" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G304" t="s">
-        <v>221</v>
+        <v>213</v>
+      </c>
+      <c r="F304" t="s">
+        <v>25</v>
+      </c>
+      <c r="H304" t="s">
+        <v>25</v>
+      </c>
+      <c r="I304" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.2">
@@ -8513,152 +8500,26 @@
         <v>10</v>
       </c>
       <c r="B305" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D305" t="s">
         <v>20</v>
       </c>
       <c r="E305" t="s">
-        <v>219</v>
-      </c>
-      <c r="F305" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G305" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
-        <v>10</v>
-      </c>
-      <c r="B306" t="s">
-        <v>62</v>
-      </c>
-      <c r="D306" t="s">
-        <v>20</v>
-      </c>
-      <c r="E306" t="s">
-        <v>219</v>
-      </c>
-      <c r="F306" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G306" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A307" t="s">
-        <v>10</v>
-      </c>
-      <c r="B307" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C307" t="b">
-        <v>1</v>
-      </c>
-      <c r="D307" t="s">
-        <v>20</v>
-      </c>
-      <c r="E307" t="s">
-        <v>219</v>
-      </c>
-      <c r="F307" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G307" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A308" t="s">
-        <v>10</v>
-      </c>
-      <c r="B308" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D308" t="s">
-        <v>20</v>
-      </c>
-      <c r="E308" t="s">
-        <v>219</v>
-      </c>
-      <c r="F308" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G308" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A309" t="s">
-        <v>10</v>
-      </c>
-      <c r="B309" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D309" t="s">
-        <v>20</v>
-      </c>
-      <c r="E309" t="s">
-        <v>219</v>
-      </c>
-      <c r="F309" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G309" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
-        <v>10</v>
-      </c>
-      <c r="B310" t="s">
-        <v>153</v>
-      </c>
-      <c r="D310" t="s">
-        <v>20</v>
-      </c>
-      <c r="E310" t="s">
-        <v>219</v>
-      </c>
-      <c r="F310" t="s">
-        <v>25</v>
-      </c>
-      <c r="H310" t="s">
-        <v>25</v>
-      </c>
-      <c r="I310" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A311" t="s">
-        <v>10</v>
-      </c>
-      <c r="B311" t="s">
-        <v>19</v>
-      </c>
-      <c r="D311" t="s">
-        <v>20</v>
-      </c>
-      <c r="E311" t="s">
-        <v>219</v>
-      </c>
-      <c r="F311" t="s">
-        <v>25</v>
-      </c>
-      <c r="H311" t="s">
-        <v>25</v>
-      </c>
-      <c r="I311" t="s">
+        <v>213</v>
+      </c>
+      <c r="F305" t="s">
+        <v>25</v>
+      </c>
+      <c r="H305" t="s">
+        <v>25</v>
+      </c>
+      <c r="I305" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K311" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}"/>
+  <autoFilter ref="A1:K305" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -8733,7 +8594,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8741,7 +8602,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">

--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7279EC7-D9A7-D14B-B738-5A6BE7ED0484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0581FB76-1163-3A4D-8F33-25F7932E03A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34420" yWindow="-6720" windowWidth="32640" windowHeight="20520" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="cog_rules" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="217">
   <si>
     <t>source</t>
   </si>
@@ -364,9 +364,6 @@
   </si>
   <si>
     <t>total_radiation_dose_unit</t>
-  </si>
-  <si>
-    <t>anatomic_site</t>
   </si>
   <si>
     <t>laterality_of_radiation_field</t>
@@ -1573,6 +1570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K305"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1583,6 +1581,7 @@
     <col min="7" max="7" width="83.6640625" customWidth="1"/>
     <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -1617,10 +1616,10 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1631,7 +1630,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -1643,7 +1642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1663,7 +1662,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1686,7 +1685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1709,7 +1708,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1720,19 +1719,19 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
         <v>208</v>
       </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1743,7 +1742,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -1755,7 +1754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1798,7 +1797,7 @@
         <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>81</v>
@@ -1807,7 +1806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -1830,7 +1829,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1841,7 +1840,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -1853,7 +1852,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1876,7 +1875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1899,10 +1898,10 @@
         <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1925,7 +1924,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1965,7 +1964,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1985,7 +1984,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2048,7 +2047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -2094,7 +2093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>51</v>
       </c>
       <c r="H24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>81</v>
@@ -2146,7 +2145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -2160,7 +2159,7 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
@@ -2169,7 +2168,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -2192,7 +2191,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -2218,10 +2217,10 @@
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2244,7 +2243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2290,7 +2289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -2307,10 +2306,10 @@
         <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -2336,7 +2335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -2353,10 +2352,10 @@
         <v>41</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -2399,7 +2398,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -2422,7 +2421,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -2433,7 +2432,7 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -2445,7 +2444,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -2465,7 +2464,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -2485,7 +2484,7 @@
         <v>51</v>
       </c>
       <c r="H39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>81</v>
@@ -2494,7 +2493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -2508,13 +2507,13 @@
         <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -2537,7 +2536,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -2563,7 +2562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -2586,7 +2585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -2626,7 +2625,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -2643,10 +2642,10 @@
         <v>35</v>
       </c>
       <c r="G46" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -2689,7 +2688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2712,7 +2711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -2735,10 +2734,10 @@
         <v>72</v>
       </c>
       <c r="I50" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -2761,7 +2760,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -2772,7 +2771,7 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -2784,7 +2783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -2807,7 +2806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -2827,7 +2826,7 @@
         <v>22</v>
       </c>
       <c r="H54" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>81</v>
@@ -2836,7 +2835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2850,16 +2849,16 @@
         <v>23</v>
       </c>
       <c r="F55" t="s">
+        <v>153</v>
+      </c>
+      <c r="G55" t="s">
         <v>154</v>
-      </c>
-      <c r="G55" t="s">
-        <v>155</v>
       </c>
       <c r="J55" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -2870,7 +2869,7 @@
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F56" t="s">
         <v>25</v>
@@ -2882,7 +2881,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -2902,13 +2901,13 @@
         <v>35</v>
       </c>
       <c r="G57" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -2928,7 +2927,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -2945,10 +2944,10 @@
         <v>35</v>
       </c>
       <c r="G59" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -2971,7 +2970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -2994,7 +2993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -3040,7 +3039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -3089,7 +3088,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -3112,7 +3111,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -3123,7 +3122,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F67" t="s">
         <v>25</v>
@@ -3135,7 +3134,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -3158,12 +3157,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
@@ -3178,7 +3177,7 @@
         <v>22</v>
       </c>
       <c r="H69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>81</v>
@@ -3187,7 +3186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -3201,13 +3200,13 @@
         <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G70" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -3218,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F71" t="s">
         <v>25</v>
@@ -3230,7 +3229,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -3256,7 +3255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -3276,7 +3275,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -3293,10 +3292,10 @@
         <v>35</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>10</v>
       </c>
@@ -3319,7 +3318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -3342,7 +3341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -3365,7 +3364,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -3411,7 +3410,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -3437,7 +3436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -3471,7 +3470,7 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F82" t="s">
         <v>25</v>
@@ -3483,7 +3482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -3506,7 +3505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -3529,7 +3528,7 @@
         <v>22</v>
       </c>
       <c r="H84" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>81</v>
@@ -3538,7 +3537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -3552,16 +3551,16 @@
         <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G85" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J85" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F86" t="s">
         <v>25</v>
@@ -3584,7 +3583,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -3604,13 +3603,13 @@
         <v>35</v>
       </c>
       <c r="G87" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>10</v>
       </c>
@@ -3630,7 +3629,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -3647,10 +3646,10 @@
         <v>35</v>
       </c>
       <c r="G89" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -3673,7 +3672,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>10</v>
       </c>
@@ -3696,7 +3695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>10</v>
       </c>
@@ -3719,7 +3718,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -3742,7 +3741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -3765,7 +3764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>10</v>
       </c>
@@ -3791,7 +3790,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>10</v>
       </c>
@@ -3814,7 +3813,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>10</v>
       </c>
@@ -3825,7 +3824,7 @@
         <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F97" t="s">
         <v>25</v>
@@ -3837,7 +3836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -3860,7 +3859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>10</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>22</v>
       </c>
       <c r="H99" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>81</v>
@@ -3889,7 +3888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -3903,13 +3902,13 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G100" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>10</v>
       </c>
@@ -3920,7 +3919,7 @@
         <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
@@ -3932,7 +3931,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -3958,7 +3957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>10</v>
       </c>
@@ -3978,10 +3977,10 @@
         <v>25</v>
       </c>
       <c r="I103" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -4004,7 +4003,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -4030,7 +4029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -4047,10 +4046,10 @@
         <v>35</v>
       </c>
       <c r="G106" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -4076,7 +4075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -4122,7 +4121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -4148,7 +4147,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -4171,7 +4170,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>10</v>
       </c>
@@ -4182,7 +4181,7 @@
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F112" t="s">
         <v>25</v>
@@ -4194,7 +4193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>10</v>
       </c>
@@ -4217,7 +4216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -4237,7 +4236,7 @@
         <v>22</v>
       </c>
       <c r="H114" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>81</v>
@@ -4246,7 +4245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -4260,7 +4259,7 @@
         <v>23</v>
       </c>
       <c r="F115" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -4269,7 +4268,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -4280,7 +4279,7 @@
         <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F116" t="s">
         <v>25</v>
@@ -4292,7 +4291,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>10</v>
       </c>
@@ -4338,10 +4337,10 @@
         <v>25</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>10</v>
       </c>
@@ -4364,7 +4363,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>10</v>
       </c>
@@ -4387,7 +4386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -4410,7 +4409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>10</v>
       </c>
@@ -4436,7 +4435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>10</v>
       </c>
@@ -4453,10 +4452,10 @@
         <v>41</v>
       </c>
       <c r="G123" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>10</v>
       </c>
@@ -4473,7 +4472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>10</v>
       </c>
@@ -4499,7 +4498,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>10</v>
       </c>
@@ -4522,7 +4521,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -4533,7 +4532,7 @@
         <v>20</v>
       </c>
       <c r="E127" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F127" t="s">
         <v>25</v>
@@ -4545,7 +4544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -4568,7 +4567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -4588,10 +4587,10 @@
         <v>50</v>
       </c>
       <c r="G129" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H129" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I129" t="s">
         <v>82</v>
@@ -4600,7 +4599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -4614,13 +4613,13 @@
         <v>23</v>
       </c>
       <c r="F130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G130" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -4631,7 +4630,7 @@
         <v>20</v>
       </c>
       <c r="E131" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F131" t="s">
         <v>25</v>
@@ -4643,7 +4642,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -4669,7 +4668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -4689,10 +4688,10 @@
         <v>25</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -4715,7 +4714,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -4738,7 +4737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -4761,7 +4760,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>10</v>
       </c>
@@ -4787,7 +4786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -4804,10 +4803,10 @@
         <v>41</v>
       </c>
       <c r="G138" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>10</v>
       </c>
@@ -4830,7 +4829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>10</v>
       </c>
@@ -4856,7 +4855,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -4879,7 +4878,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -4890,7 +4889,7 @@
         <v>20</v>
       </c>
       <c r="E142" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F142" t="s">
         <v>25</v>
@@ -4902,7 +4901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -4925,7 +4924,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -4942,10 +4941,10 @@
         <v>13</v>
       </c>
       <c r="G144" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H144" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I144" t="s">
         <v>82</v>
@@ -4954,7 +4953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -4968,7 +4967,7 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G145" t="s">
         <v>24</v>
@@ -4977,7 +4976,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -4988,7 +4987,7 @@
         <v>20</v>
       </c>
       <c r="E146" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F146" t="s">
         <v>25</v>
@@ -5000,7 +4999,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -5026,7 +5025,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -5049,7 +5048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -5069,7 +5068,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -5115,7 +5114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -5141,7 +5140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>10</v>
       </c>
@@ -5161,7 +5160,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>10</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>10</v>
       </c>
@@ -5210,7 +5209,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -5233,18 +5232,18 @@
         <v>55</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D157" t="s">
         <v>20</v>
       </c>
       <c r="E157" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F157" t="s">
         <v>25</v>
@@ -5256,12 +5255,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>10</v>
       </c>
       <c r="B158" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D158" t="s">
         <v>20</v>
@@ -5279,7 +5278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -5296,10 +5295,10 @@
         <v>50</v>
       </c>
       <c r="G159" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H159" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I159" t="s">
         <v>82</v>
@@ -5308,12 +5307,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D160" t="s">
         <v>20</v>
@@ -5322,24 +5321,24 @@
         <v>23</v>
       </c>
       <c r="F160" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G160" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>10</v>
       </c>
       <c r="B161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D161" t="s">
         <v>20</v>
       </c>
       <c r="E161" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F161" t="s">
         <v>25</v>
@@ -5351,12 +5350,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>10</v>
       </c>
       <c r="B162" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C162" t="b">
         <v>1</v>
@@ -5371,18 +5370,18 @@
         <v>35</v>
       </c>
       <c r="G162" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J162" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>10</v>
       </c>
       <c r="B163" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D163" t="s">
         <v>20</v>
@@ -5397,12 +5396,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>10</v>
       </c>
       <c r="B164" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D164" t="s">
         <v>20</v>
@@ -5414,15 +5413,15 @@
         <v>35</v>
       </c>
       <c r="G164" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>10</v>
       </c>
       <c r="B165" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D165" t="s">
         <v>20</v>
@@ -5440,12 +5439,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D166" t="s">
         <v>20</v>
@@ -5463,12 +5462,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D167" t="s">
         <v>20</v>
@@ -5486,12 +5485,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D168" t="s">
         <v>20</v>
@@ -5509,12 +5508,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D169" t="s">
         <v>20</v>
@@ -5532,12 +5531,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D170" t="s">
         <v>20</v>
@@ -5558,12 +5557,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>10</v>
       </c>
       <c r="B171" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
@@ -5581,18 +5580,18 @@
         <v>55</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>10</v>
       </c>
       <c r="B172" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D172" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E172" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F172" t="s">
         <v>25</v>
@@ -5601,18 +5600,18 @@
         <v>25</v>
       </c>
       <c r="I172" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D173" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>71</v>
@@ -5624,151 +5623,154 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D174" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F174" t="s">
         <v>73</v>
       </c>
       <c r="G174" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H174" t="s">
         <v>80</v>
       </c>
       <c r="I174" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>10</v>
       </c>
       <c r="B175" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C175" t="b">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
       </c>
       <c r="G175" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>10</v>
       </c>
       <c r="B176" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D176" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E176" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F176" t="s">
+        <v>153</v>
+      </c>
+      <c r="G176" t="s">
+        <v>165</v>
+      </c>
+      <c r="J176">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>10</v>
+      </c>
+      <c r="B177" t="s">
+        <v>134</v>
+      </c>
+      <c r="D177" t="s">
+        <v>134</v>
+      </c>
+      <c r="E177" t="s">
         <v>130</v>
-      </c>
-      <c r="F176" t="s">
-        <v>154</v>
-      </c>
-      <c r="G176" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
-        <v>10</v>
-      </c>
-      <c r="B177" t="s">
-        <v>135</v>
-      </c>
-      <c r="D177" t="s">
-        <v>135</v>
-      </c>
-      <c r="E177" t="s">
-        <v>131</v>
       </c>
       <c r="F177" t="s">
         <v>35</v>
       </c>
       <c r="G177" t="s">
+        <v>163</v>
+      </c>
+      <c r="K177" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>10</v>
+      </c>
+      <c r="B178" t="s">
+        <v>134</v>
+      </c>
+      <c r="D178" t="s">
+        <v>134</v>
+      </c>
+      <c r="E178" t="s">
+        <v>131</v>
+      </c>
+      <c r="F178" t="s">
+        <v>160</v>
+      </c>
+      <c r="G178" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>10</v>
+      </c>
+      <c r="B179" t="s">
+        <v>134</v>
+      </c>
+      <c r="D179" t="s">
+        <v>134</v>
+      </c>
+      <c r="E179" t="s">
+        <v>132</v>
+      </c>
+      <c r="F179" t="s">
+        <v>159</v>
+      </c>
+      <c r="G179" t="s">
         <v>164</v>
       </c>
-      <c r="K177" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A178" t="s">
-        <v>10</v>
-      </c>
-      <c r="B178" t="s">
-        <v>135</v>
-      </c>
-      <c r="D178" t="s">
-        <v>135</v>
-      </c>
-      <c r="E178" t="s">
-        <v>132</v>
-      </c>
-      <c r="F178" t="s">
-        <v>161</v>
-      </c>
-      <c r="G178" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
-        <v>10</v>
-      </c>
-      <c r="B179" t="s">
-        <v>135</v>
-      </c>
-      <c r="D179" t="s">
-        <v>135</v>
-      </c>
-      <c r="E179" t="s">
+    </row>
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>10</v>
+      </c>
+      <c r="B180" t="s">
+        <v>134</v>
+      </c>
+      <c r="D180" t="s">
+        <v>134</v>
+      </c>
+      <c r="E180" t="s">
         <v>133</v>
       </c>
-      <c r="F179" t="s">
-        <v>160</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
-        <v>10</v>
-      </c>
-      <c r="B180" t="s">
-        <v>135</v>
-      </c>
-      <c r="D180" t="s">
-        <v>135</v>
-      </c>
-      <c r="E180" t="s">
-        <v>134</v>
-      </c>
       <c r="F180" t="s">
         <v>25</v>
       </c>
@@ -5776,18 +5778,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>10</v>
       </c>
       <c r="B181" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D181" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E181" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F181" t="s">
         <v>25</v>
@@ -5796,18 +5798,18 @@
         <v>25</v>
       </c>
       <c r="I181" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>10</v>
       </c>
       <c r="B182" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D182" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>71</v>
@@ -5819,70 +5821,70 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>10</v>
       </c>
       <c r="B183" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D183" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F183" t="s">
         <v>73</v>
       </c>
       <c r="G183" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H183" t="s">
+        <v>169</v>
+      </c>
+      <c r="I183" t="s">
         <v>170</v>
       </c>
-      <c r="I183" t="s">
-        <v>171</v>
-      </c>
       <c r="J183" t="s">
         <v>17</v>
       </c>
       <c r="K183" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>10</v>
       </c>
       <c r="B184" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D184" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E184" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F184" t="s">
+        <v>173</v>
+      </c>
+      <c r="G184" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>10</v>
+      </c>
+      <c r="B185" t="s">
+        <v>126</v>
+      </c>
+      <c r="D185" t="s">
+        <v>126</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="F184" t="s">
-        <v>174</v>
-      </c>
-      <c r="G184" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
-        <v>10</v>
-      </c>
-      <c r="B185" t="s">
-        <v>127</v>
-      </c>
-      <c r="D185" t="s">
-        <v>127</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="F185" t="s">
         <v>25</v>
@@ -5894,42 +5896,42 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>10</v>
       </c>
       <c r="B186" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D186" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E186" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F186" t="s">
+        <v>25</v>
+      </c>
+      <c r="H186" t="s">
+        <v>25</v>
+      </c>
+      <c r="I186" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>10</v>
+      </c>
+      <c r="B187" t="s">
+        <v>126</v>
+      </c>
+      <c r="D187" t="s">
+        <v>126</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F186" t="s">
-        <v>25</v>
-      </c>
-      <c r="H186" t="s">
-        <v>25</v>
-      </c>
-      <c r="I186" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
-        <v>10</v>
-      </c>
-      <c r="B187" t="s">
-        <v>127</v>
-      </c>
-      <c r="D187" t="s">
-        <v>127</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="F187" t="s">
         <v>25</v>
       </c>
@@ -5940,18 +5942,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>10</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D188" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E188" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F188" t="s">
         <v>25</v>
@@ -5960,18 +5962,18 @@
         <v>25</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>10</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D189" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>71</v>
@@ -5983,15 +5985,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>10</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D190" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>104</v>
@@ -6006,18 +6008,18 @@
         <v>72</v>
       </c>
       <c r="I190" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>10</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D191" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>92</v>
@@ -6029,21 +6031,21 @@
         <v>25</v>
       </c>
       <c r="I191" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>10</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C192" t="b">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>105</v>
@@ -6052,24 +6054,24 @@
         <v>35</v>
       </c>
       <c r="G192" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H192" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I192" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>10</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D193" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>93</v>
@@ -6084,15 +6086,15 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>10</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D194" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>94</v>
@@ -6110,15 +6112,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>10</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D195" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>106</v>
@@ -6127,18 +6129,18 @@
         <v>35</v>
       </c>
       <c r="G195" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>10</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D196" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E196" t="s">
         <v>107</v>
@@ -6150,15 +6152,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>10</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D197" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E197" t="s">
         <v>108</v>
@@ -6170,15 +6172,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>10</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D198" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>32</v>
@@ -6193,15 +6195,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>10</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D199" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>32</v>
@@ -6213,121 +6215,121 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>10</v>
       </c>
       <c r="B200" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D200" t="s">
+        <v>113</v>
+      </c>
+      <c r="E200" t="s">
+        <v>109</v>
+      </c>
+      <c r="F200" t="s">
+        <v>25</v>
+      </c>
+      <c r="H200" t="s">
+        <v>25</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>10</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D201" t="s">
+        <v>113</v>
+      </c>
+      <c r="E201" t="s">
+        <v>110</v>
+      </c>
+      <c r="F201" t="s">
+        <v>25</v>
+      </c>
+      <c r="H201" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>10</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D202" t="s">
+        <v>113</v>
+      </c>
+      <c r="E202" t="s">
+        <v>111</v>
+      </c>
+      <c r="F202" t="s">
+        <v>25</v>
+      </c>
+      <c r="H202" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>10</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D203" t="s">
+        <v>113</v>
+      </c>
+      <c r="E203" t="s">
+        <v>112</v>
+      </c>
+      <c r="F203" t="s">
+        <v>25</v>
+      </c>
+      <c r="H203" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>10</v>
+      </c>
+      <c r="B204" t="s">
         <v>114</v>
       </c>
-      <c r="D200" t="s">
+      <c r="D204" t="s">
         <v>114</v>
       </c>
-      <c r="E200" t="s">
-        <v>110</v>
-      </c>
-      <c r="F200" t="s">
-        <v>25</v>
-      </c>
-      <c r="H200" t="s">
-        <v>25</v>
-      </c>
-      <c r="I200" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A201" t="s">
-        <v>10</v>
-      </c>
-      <c r="B201" s="2" t="s">
+      <c r="E204" t="s">
+        <v>209</v>
+      </c>
+      <c r="F204" t="s">
+        <v>25</v>
+      </c>
+      <c r="H204" t="s">
+        <v>25</v>
+      </c>
+      <c r="I204" t="s">
         <v>114</v>
       </c>
-      <c r="D201" t="s">
+    </row>
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>10</v>
+      </c>
+      <c r="B205" t="s">
         <v>114</v>
       </c>
-      <c r="E201" t="s">
-        <v>111</v>
-      </c>
-      <c r="F201" t="s">
-        <v>25</v>
-      </c>
-      <c r="H201" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A202" t="s">
-        <v>10</v>
-      </c>
-      <c r="B202" s="2" t="s">
+      <c r="D205" t="s">
         <v>114</v>
-      </c>
-      <c r="D202" t="s">
-        <v>114</v>
-      </c>
-      <c r="E202" t="s">
-        <v>112</v>
-      </c>
-      <c r="F202" t="s">
-        <v>25</v>
-      </c>
-      <c r="H202" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A203" t="s">
-        <v>10</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D203" t="s">
-        <v>114</v>
-      </c>
-      <c r="E203" t="s">
-        <v>113</v>
-      </c>
-      <c r="F203" t="s">
-        <v>25</v>
-      </c>
-      <c r="H203" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
-        <v>10</v>
-      </c>
-      <c r="B204" t="s">
-        <v>115</v>
-      </c>
-      <c r="D204" t="s">
-        <v>115</v>
-      </c>
-      <c r="E204" t="s">
-        <v>210</v>
-      </c>
-      <c r="F204" t="s">
-        <v>25</v>
-      </c>
-      <c r="H204" t="s">
-        <v>25</v>
-      </c>
-      <c r="I204" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A205" t="s">
-        <v>10</v>
-      </c>
-      <c r="B205" t="s">
-        <v>115</v>
-      </c>
-      <c r="D205" t="s">
-        <v>115</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>71</v>
@@ -6339,18 +6341,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>10</v>
       </c>
       <c r="B206" t="s">
+        <v>114</v>
+      </c>
+      <c r="D206" t="s">
+        <v>114</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D206" t="s">
-        <v>115</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="F206" t="s">
         <v>13</v>
@@ -6362,18 +6364,18 @@
         <v>72</v>
       </c>
       <c r="I206" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>10</v>
       </c>
       <c r="B207" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D207" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>92</v>
@@ -6388,38 +6390,38 @@
         <v>53</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>10</v>
       </c>
       <c r="B208" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C208" t="b">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>10</v>
       </c>
       <c r="B209" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D209" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>93</v>
@@ -6434,15 +6436,15 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>10</v>
       </c>
       <c r="B210" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D210" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>94</v>
@@ -6462,13 +6464,13 @@
         <v>10</v>
       </c>
       <c r="B211" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D211" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E211" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F211" t="s">
         <v>25</v>
@@ -6477,7 +6479,7 @@
         <v>25</v>
       </c>
       <c r="I211" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.2">
@@ -6485,10 +6487,10 @@
         <v>10</v>
       </c>
       <c r="B212" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D212" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>71</v>
@@ -6505,13 +6507,13 @@
         <v>10</v>
       </c>
       <c r="B213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F213" t="s">
         <v>13</v>
@@ -6523,7 +6525,7 @@
         <v>72</v>
       </c>
       <c r="I213" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.2">
@@ -6531,10 +6533,10 @@
         <v>10</v>
       </c>
       <c r="B214" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D214" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>92</v>
@@ -6546,10 +6548,10 @@
         <v>25</v>
       </c>
       <c r="I214" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J214" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.2">
@@ -6557,25 +6559,25 @@
         <v>10</v>
       </c>
       <c r="B215" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C215" t="b">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F215" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G215" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J215" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.2">
@@ -6583,19 +6585,19 @@
         <v>10</v>
       </c>
       <c r="B216" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D216" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F216" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G216" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J216">
         <v>-999</v>
@@ -6606,19 +6608,19 @@
         <v>10</v>
       </c>
       <c r="B217" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D217" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F217" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G217" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J217">
         <v>-999</v>
@@ -6629,13 +6631,13 @@
         <v>10</v>
       </c>
       <c r="B218" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D218" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="F218" t="s">
         <v>25</v>
@@ -6652,36 +6654,36 @@
         <v>10</v>
       </c>
       <c r="B219" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D219" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G219" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I219" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>10</v>
       </c>
       <c r="B220" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D220" t="s">
         <v>103</v>
       </c>
       <c r="E220" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F220" t="s">
         <v>25</v>
@@ -6693,12 +6695,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>10</v>
       </c>
       <c r="B221" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D221" t="s">
         <v>103</v>
@@ -6713,12 +6715,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>10</v>
       </c>
       <c r="B222" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D222" t="s">
         <v>103</v>
@@ -6736,15 +6738,15 @@
         <v>72</v>
       </c>
       <c r="I222" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>10</v>
       </c>
       <c r="B223" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D223" t="s">
         <v>103</v>
@@ -6759,21 +6761,21 @@
         <v>25</v>
       </c>
       <c r="I223" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>10</v>
       </c>
       <c r="B224" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D224" t="s">
         <v>103</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F224" t="s">
         <v>25</v>
@@ -6782,15 +6784,15 @@
         <v>25</v>
       </c>
       <c r="I224" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>10</v>
       </c>
       <c r="B225" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D225" t="s">
         <v>103</v>
@@ -6808,12 +6810,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>10</v>
       </c>
       <c r="B226" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D226" t="s">
         <v>103</v>
@@ -6831,12 +6833,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>10</v>
       </c>
       <c r="B227" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C227" t="b">
         <v>1</v>
@@ -6851,15 +6853,15 @@
         <v>35</v>
       </c>
       <c r="G227" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>10</v>
       </c>
       <c r="B228" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D228" t="s">
         <v>103</v>
@@ -6874,12 +6876,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>10</v>
       </c>
       <c r="B229" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D229" t="s">
         <v>103</v>
@@ -6894,12 +6896,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>10</v>
       </c>
       <c r="B230" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D230" t="s">
         <v>103</v>
@@ -6914,12 +6916,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>10</v>
       </c>
       <c r="B231" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D231" t="s">
         <v>103</v>
@@ -6934,12 +6936,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>10</v>
       </c>
       <c r="B232" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D232" t="s">
         <v>103</v>
@@ -6954,12 +6956,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>10</v>
       </c>
       <c r="B233" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D233" t="s">
         <v>103</v>
@@ -6974,12 +6976,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>10</v>
       </c>
       <c r="B234" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D234" t="s">
         <v>103</v>
@@ -6994,18 +6996,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D235" t="s">
         <v>103</v>
       </c>
       <c r="E235" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F235" t="s">
         <v>25</v>
@@ -7017,12 +7019,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>10</v>
       </c>
       <c r="B236" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D236" t="s">
         <v>103</v>
@@ -7037,12 +7039,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D237" t="s">
         <v>103</v>
@@ -7060,15 +7062,15 @@
         <v>72</v>
       </c>
       <c r="I237" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>10</v>
       </c>
       <c r="B238" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D238" t="s">
         <v>103</v>
@@ -7083,21 +7085,21 @@
         <v>25</v>
       </c>
       <c r="I238" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>10</v>
       </c>
       <c r="B239" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D239" t="s">
         <v>103</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F239" t="s">
         <v>25</v>
@@ -7106,15 +7108,15 @@
         <v>25</v>
       </c>
       <c r="I239" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>10</v>
       </c>
       <c r="B240" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D240" t="s">
         <v>103</v>
@@ -7132,12 +7134,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>10</v>
       </c>
       <c r="B241" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D241" t="s">
         <v>103</v>
@@ -7155,12 +7157,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>10</v>
       </c>
       <c r="B242" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C242" t="b">
         <v>1</v>
@@ -7175,15 +7177,15 @@
         <v>35</v>
       </c>
       <c r="G242" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>10</v>
       </c>
       <c r="B243" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D243" t="s">
         <v>103</v>
@@ -7198,12 +7200,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>10</v>
       </c>
       <c r="B244" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D244" t="s">
         <v>103</v>
@@ -7218,12 +7220,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>10</v>
       </c>
       <c r="B245" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D245" t="s">
         <v>103</v>
@@ -7238,12 +7240,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>10</v>
       </c>
       <c r="B246" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D246" t="s">
         <v>103</v>
@@ -7258,12 +7260,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>10</v>
       </c>
       <c r="B247" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D247" t="s">
         <v>103</v>
@@ -7278,12 +7280,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>10</v>
       </c>
       <c r="B248" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D248" t="s">
         <v>103</v>
@@ -7298,12 +7300,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D249" t="s">
         <v>103</v>
@@ -7318,18 +7320,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>10</v>
       </c>
       <c r="B250" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D250" t="s">
         <v>103</v>
       </c>
       <c r="E250" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F250" t="s">
         <v>25</v>
@@ -7341,12 +7343,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>10</v>
       </c>
       <c r="B251" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D251" t="s">
         <v>103</v>
@@ -7361,12 +7363,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>10</v>
       </c>
       <c r="B252" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D252" t="s">
         <v>103</v>
@@ -7384,15 +7386,15 @@
         <v>72</v>
       </c>
       <c r="I252" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>10</v>
+      </c>
+      <c r="B253" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A253" t="s">
-        <v>10</v>
-      </c>
-      <c r="B253" t="s">
-        <v>195</v>
       </c>
       <c r="D253" t="s">
         <v>103</v>
@@ -7407,21 +7409,21 @@
         <v>25</v>
       </c>
       <c r="I253" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>10</v>
       </c>
       <c r="B254" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D254" t="s">
         <v>103</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F254" t="s">
         <v>25</v>
@@ -7430,15 +7432,15 @@
         <v>25</v>
       </c>
       <c r="I254" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>10</v>
       </c>
       <c r="B255" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D255" t="s">
         <v>103</v>
@@ -7456,12 +7458,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D256" t="s">
         <v>103</v>
@@ -7479,12 +7481,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C257" t="b">
         <v>1</v>
@@ -7499,15 +7501,15 @@
         <v>35</v>
       </c>
       <c r="G257" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>10</v>
       </c>
       <c r="B258" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D258" t="s">
         <v>103</v>
@@ -7522,12 +7524,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>10</v>
       </c>
       <c r="B259" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D259" t="s">
         <v>103</v>
@@ -7542,12 +7544,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D260" t="s">
         <v>103</v>
@@ -7562,12 +7564,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>10</v>
       </c>
       <c r="B261" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D261" t="s">
         <v>103</v>
@@ -7582,12 +7584,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>10</v>
       </c>
       <c r="B262" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D262" t="s">
         <v>103</v>
@@ -7602,12 +7604,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>10</v>
       </c>
       <c r="B263" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D263" t="s">
         <v>103</v>
@@ -7622,12 +7624,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>10</v>
       </c>
       <c r="B264" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D264" t="s">
         <v>103</v>
@@ -7642,18 +7644,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>10</v>
       </c>
       <c r="B265" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D265" t="s">
         <v>103</v>
       </c>
       <c r="E265" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F265" t="s">
         <v>25</v>
@@ -7665,12 +7667,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>10</v>
       </c>
       <c r="B266" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D266" t="s">
         <v>103</v>
@@ -7685,12 +7687,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>10</v>
       </c>
       <c r="B267" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D267" t="s">
         <v>103</v>
@@ -7708,15 +7710,15 @@
         <v>72</v>
       </c>
       <c r="I267" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>10</v>
       </c>
       <c r="B268" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D268" t="s">
         <v>103</v>
@@ -7731,21 +7733,21 @@
         <v>25</v>
       </c>
       <c r="I268" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>10</v>
       </c>
       <c r="B269" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D269" t="s">
         <v>103</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F269" t="s">
         <v>25</v>
@@ -7754,15 +7756,15 @@
         <v>25</v>
       </c>
       <c r="I269" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>10</v>
       </c>
       <c r="B270" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D270" t="s">
         <v>103</v>
@@ -7780,12 +7782,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>10</v>
       </c>
       <c r="B271" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D271" t="s">
         <v>103</v>
@@ -7803,12 +7805,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>10</v>
       </c>
       <c r="B272" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C272" t="b">
         <v>1</v>
@@ -7823,15 +7825,15 @@
         <v>35</v>
       </c>
       <c r="G272" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>10</v>
       </c>
       <c r="B273" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D273" t="s">
         <v>103</v>
@@ -7846,12 +7848,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>10</v>
       </c>
       <c r="B274" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D274" t="s">
         <v>103</v>
@@ -7866,12 +7868,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>10</v>
       </c>
       <c r="B275" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D275" t="s">
         <v>103</v>
@@ -7886,12 +7888,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>10</v>
       </c>
       <c r="B276" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D276" t="s">
         <v>103</v>
@@ -7906,12 +7908,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>10</v>
       </c>
       <c r="B277" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D277" t="s">
         <v>103</v>
@@ -7926,12 +7928,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>10</v>
       </c>
       <c r="B278" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D278" t="s">
         <v>103</v>
@@ -7946,12 +7948,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>10</v>
       </c>
       <c r="B279" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D279" t="s">
         <v>103</v>
@@ -7966,18 +7968,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>10</v>
       </c>
       <c r="B280" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D280" t="s">
         <v>103</v>
       </c>
       <c r="E280" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F280" t="s">
         <v>25</v>
@@ -7989,12 +7991,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>10</v>
       </c>
       <c r="B281" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D281" t="s">
         <v>103</v>
@@ -8009,12 +8011,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>10</v>
       </c>
       <c r="B282" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D282" t="s">
         <v>103</v>
@@ -8023,20 +8025,20 @@
         <v>91</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>10</v>
       </c>
       <c r="B283" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D283" t="s">
         <v>103</v>
@@ -8051,35 +8053,35 @@
         <v>25</v>
       </c>
       <c r="I283" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>10</v>
       </c>
       <c r="B284" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D284" t="s">
         <v>103</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F284" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G284" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>10</v>
       </c>
       <c r="B285" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D285" t="s">
         <v>103</v>
@@ -8097,12 +8099,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>10</v>
       </c>
       <c r="B286" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D286" t="s">
         <v>103</v>
@@ -8120,12 +8122,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>10</v>
       </c>
       <c r="B287" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C287" t="b">
         <v>1</v>
@@ -8140,15 +8142,15 @@
         <v>13</v>
       </c>
       <c r="G287" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>10</v>
       </c>
       <c r="B288" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D288" t="s">
         <v>103</v>
@@ -8163,12 +8165,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>10</v>
       </c>
       <c r="B289" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D289" t="s">
         <v>103</v>
@@ -8183,12 +8185,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>10</v>
       </c>
       <c r="B290" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D290" t="s">
         <v>103</v>
@@ -8203,12 +8205,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>10</v>
       </c>
       <c r="B291" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D291" t="s">
         <v>103</v>
@@ -8223,12 +8225,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>10</v>
       </c>
       <c r="B292" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D292" t="s">
         <v>103</v>
@@ -8243,12 +8245,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>10</v>
       </c>
       <c r="B293" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D293" t="s">
         <v>103</v>
@@ -8263,12 +8265,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>10</v>
       </c>
       <c r="B294" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D294" t="s">
         <v>103</v>
@@ -8283,7 +8285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>10</v>
       </c>
@@ -8297,16 +8299,16 @@
         <v>20</v>
       </c>
       <c r="E295" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F295" t="s">
         <v>50</v>
       </c>
       <c r="G295" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>10</v>
       </c>
@@ -8317,16 +8319,16 @@
         <v>20</v>
       </c>
       <c r="E296" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F296" t="s">
         <v>50</v>
       </c>
       <c r="G296" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>10</v>
       </c>
@@ -8337,16 +8339,16 @@
         <v>20</v>
       </c>
       <c r="E297" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F297" t="s">
         <v>50</v>
       </c>
       <c r="G297" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>10</v>
       </c>
@@ -8360,16 +8362,16 @@
         <v>20</v>
       </c>
       <c r="E298" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F298" t="s">
         <v>50</v>
       </c>
       <c r="G298" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>10</v>
       </c>
@@ -8380,16 +8382,16 @@
         <v>20</v>
       </c>
       <c r="E299" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F299" t="s">
         <v>50</v>
       </c>
       <c r="G299" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>10</v>
       </c>
@@ -8400,16 +8402,16 @@
         <v>20</v>
       </c>
       <c r="E300" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F300" t="s">
         <v>50</v>
       </c>
       <c r="G300" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>10</v>
       </c>
@@ -8423,7 +8425,7 @@
         <v>20</v>
       </c>
       <c r="E301" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F301" t="s">
         <v>50</v>
@@ -8432,7 +8434,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>10</v>
       </c>
@@ -8443,7 +8445,7 @@
         <v>20</v>
       </c>
       <c r="E302" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F302" t="s">
         <v>50</v>
@@ -8452,7 +8454,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>10</v>
       </c>
@@ -8463,7 +8465,7 @@
         <v>20</v>
       </c>
       <c r="E303" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F303" t="s">
         <v>50</v>
@@ -8472,18 +8474,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>10</v>
       </c>
       <c r="B304" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D304" t="s">
         <v>20</v>
       </c>
       <c r="E304" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F304" t="s">
         <v>25</v>
@@ -8495,7 +8497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>10</v>
       </c>
@@ -8506,7 +8508,7 @@
         <v>20</v>
       </c>
       <c r="E305" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F305" t="s">
         <v>25</v>
@@ -8519,7 +8521,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K305" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}"/>
+  <autoFilter ref="A1:K305" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="treatment_surgery"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -8594,7 +8602,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -8602,7 +8610,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
